--- a/public/frame.xlsx
+++ b/public/frame.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E592CA-1A5A-44FD-A232-48440642E8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD51B83B-68E5-4028-B92F-137E05561B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" tabRatio="661" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="661" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시간표" sheetId="83" r:id="rId1"/>
@@ -31,15 +31,14 @@
     <sheet name="nightSchedule" sheetId="5" state="hidden" r:id="rId21"/>
     <sheet name="groupCount" sheetId="84" state="hidden" r:id="rId22"/>
     <sheet name="totalSchedule" sheetId="6" state="hidden" r:id="rId23"/>
-    <sheet name="groupSchedule" sheetId="7" state="hidden" r:id="rId24"/>
-    <sheet name="dayWorkCount" sheetId="8" state="hidden" r:id="rId25"/>
-    <sheet name="dayGroupCount" sheetId="10" state="hidden" r:id="rId26"/>
-    <sheet name="nightGroupCount" sheetId="11" state="hidden" r:id="rId27"/>
-    <sheet name="base" sheetId="12" state="hidden" r:id="rId28"/>
+    <sheet name="dayWorkCount" sheetId="8" state="hidden" r:id="rId24"/>
+    <sheet name="dayGroupCount" sheetId="10" state="hidden" r:id="rId25"/>
+    <sheet name="nightGroupCount" sheetId="11" state="hidden" r:id="rId26"/>
+    <sheet name="base" sheetId="12" state="hidden" r:id="rId27"/>
   </sheets>
   <externalReferences>
+    <externalReference r:id="rId28"/>
     <externalReference r:id="rId29"/>
-    <externalReference r:id="rId30"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">시간표!$A1:$AI20</definedName>
@@ -1351,6 +1350,18 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1358,9 +1369,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1423,13 +1431,79 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="12" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1491,81 +1565,6 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6287,42 +6286,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48">
-      <c r="A1" s="106" t="str">
+      <c r="A1" s="82" t="str">
         <f>""&amp;default!A1&amp;"월 사회복무요원 근무계획"</f>
         <v>월 사회복무요원 근무계획</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
-      <c r="AC1" s="106"/>
-      <c r="AD1" s="106"/>
-      <c r="AE1" s="106"/>
-      <c r="AF1" s="106"/>
-      <c r="AG1" s="106"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="82"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="82"/>
+      <c r="U1" s="82"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="82"/>
+      <c r="X1" s="82"/>
+      <c r="Y1" s="82"/>
+      <c r="Z1" s="82"/>
+      <c r="AA1" s="82"/>
+      <c r="AB1" s="82"/>
+      <c r="AC1" s="82"/>
+      <c r="AD1" s="82"/>
+      <c r="AE1" s="82"/>
+      <c r="AF1" s="82"/>
+      <c r="AG1" s="82"/>
       <c r="AH1" s="1"/>
       <c r="AI1" s="2"/>
       <c r="AJ1" s="1"/>
@@ -6331,39 +6330,39 @@
       <c r="AM1" s="1"/>
     </row>
     <row r="2" spans="1:48">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="106"/>
-      <c r="I2" s="106"/>
-      <c r="J2" s="106"/>
-      <c r="K2" s="106"/>
-      <c r="L2" s="106"/>
-      <c r="M2" s="106"/>
-      <c r="N2" s="106"/>
-      <c r="O2" s="106"/>
-      <c r="P2" s="106"/>
-      <c r="Q2" s="106"/>
-      <c r="R2" s="106"/>
-      <c r="S2" s="106"/>
-      <c r="T2" s="106"/>
-      <c r="U2" s="106"/>
-      <c r="V2" s="106"/>
-      <c r="W2" s="106"/>
-      <c r="X2" s="106"/>
-      <c r="Y2" s="106"/>
-      <c r="Z2" s="106"/>
-      <c r="AA2" s="106"/>
-      <c r="AB2" s="106"/>
-      <c r="AC2" s="106"/>
-      <c r="AD2" s="106"/>
-      <c r="AE2" s="106"/>
-      <c r="AF2" s="106"/>
-      <c r="AG2" s="106"/>
+      <c r="A2" s="82"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82"/>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="82"/>
+      <c r="S2" s="82"/>
+      <c r="T2" s="82"/>
+      <c r="U2" s="82"/>
+      <c r="V2" s="82"/>
+      <c r="W2" s="82"/>
+      <c r="X2" s="82"/>
+      <c r="Y2" s="82"/>
+      <c r="Z2" s="82"/>
+      <c r="AA2" s="82"/>
+      <c r="AB2" s="82"/>
+      <c r="AC2" s="82"/>
+      <c r="AD2" s="82"/>
+      <c r="AE2" s="82"/>
+      <c r="AF2" s="82"/>
+      <c r="AG2" s="82"/>
       <c r="AH2" s="1"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="1"/>
@@ -6372,39 +6371,39 @@
       <c r="AM2" s="1"/>
     </row>
     <row r="3" spans="1:48" ht="8.1" customHeight="1">
-      <c r="A3" s="107"/>
-      <c r="B3" s="107"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="107"/>
-      <c r="L3" s="107"/>
-      <c r="M3" s="107"/>
-      <c r="N3" s="107"/>
-      <c r="O3" s="107"/>
-      <c r="P3" s="107"/>
-      <c r="Q3" s="107"/>
-      <c r="R3" s="107"/>
-      <c r="S3" s="107"/>
-      <c r="T3" s="107"/>
-      <c r="U3" s="107"/>
-      <c r="V3" s="107"/>
-      <c r="W3" s="107"/>
-      <c r="X3" s="107"/>
-      <c r="Y3" s="107"/>
-      <c r="Z3" s="107"/>
-      <c r="AA3" s="107"/>
-      <c r="AB3" s="107"/>
-      <c r="AC3" s="107"/>
-      <c r="AD3" s="107"/>
-      <c r="AE3" s="107"/>
-      <c r="AF3" s="107"/>
-      <c r="AG3" s="107"/>
+      <c r="A3" s="83"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="83"/>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="83"/>
+      <c r="S3" s="83"/>
+      <c r="T3" s="83"/>
+      <c r="U3" s="83"/>
+      <c r="V3" s="83"/>
+      <c r="W3" s="83"/>
+      <c r="X3" s="83"/>
+      <c r="Y3" s="83"/>
+      <c r="Z3" s="83"/>
+      <c r="AA3" s="83"/>
+      <c r="AB3" s="83"/>
+      <c r="AC3" s="83"/>
+      <c r="AD3" s="83"/>
+      <c r="AE3" s="83"/>
+      <c r="AF3" s="83"/>
+      <c r="AG3" s="83"/>
       <c r="AH3" s="3"/>
       <c r="AI3" s="4"/>
       <c r="AJ3" s="5"/>
@@ -6413,10 +6412,10 @@
       <c r="AM3" s="5"/>
     </row>
     <row r="4" spans="1:48">
-      <c r="A4" s="108" t="s">
+      <c r="A4" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="108" t="s">
+      <c r="B4" s="84" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="7"/>
@@ -6460,13 +6459,13 @@
         <v>3</v>
       </c>
       <c r="AM4" s="5"/>
-      <c r="AN4" s="86" t="s">
+      <c r="AN4" s="89" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:48">
-      <c r="A5" s="108"/>
-      <c r="B5" s="108"/>
+      <c r="A5" s="84"/>
+      <c r="B5" s="84"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -6504,7 +6503,7 @@
       <c r="AK5" s="85"/>
       <c r="AL5" s="85"/>
       <c r="AM5" s="5"/>
-      <c r="AN5" s="87"/>
+      <c r="AN5" s="90"/>
     </row>
     <row r="6" spans="1:48">
       <c r="A6" s="6"/>
@@ -7445,130 +7444,37 @@
       <c r="B22" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="6">
-        <f>groupSchedule!A1</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="6">
-        <f>groupSchedule!B1</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="6">
-        <f>groupSchedule!C1</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
-        <f>groupSchedule!D1</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="6">
-        <f>groupSchedule!E1</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="6">
-        <f>groupSchedule!F1</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="6">
-        <f>groupSchedule!G1</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="6">
-        <f>groupSchedule!H1</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="6">
-        <f>groupSchedule!I1</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="6">
-        <f>groupSchedule!J1</f>
-        <v>0</v>
-      </c>
-      <c r="M22" s="6">
-        <f>groupSchedule!K1</f>
-        <v>0</v>
-      </c>
-      <c r="N22" s="6">
-        <f>groupSchedule!L1</f>
-        <v>0</v>
-      </c>
-      <c r="O22" s="6">
-        <f>groupSchedule!M1</f>
-        <v>0</v>
-      </c>
-      <c r="P22" s="6">
-        <f>groupSchedule!N1</f>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="6">
-        <f>groupSchedule!O1</f>
-        <v>0</v>
-      </c>
-      <c r="R22" s="6">
-        <f>groupSchedule!P1</f>
-        <v>0</v>
-      </c>
-      <c r="S22" s="6">
-        <f>groupSchedule!Q1</f>
-        <v>0</v>
-      </c>
-      <c r="T22" s="6">
-        <f>groupSchedule!R1</f>
-        <v>0</v>
-      </c>
-      <c r="U22" s="6">
-        <f>groupSchedule!S1</f>
-        <v>0</v>
-      </c>
-      <c r="V22" s="6">
-        <f>groupSchedule!T1</f>
-        <v>0</v>
-      </c>
-      <c r="W22" s="6">
-        <f>groupSchedule!U1</f>
-        <v>0</v>
-      </c>
-      <c r="X22" s="6">
-        <f>groupSchedule!V1</f>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="6">
-        <f>groupSchedule!W1</f>
-        <v>0</v>
-      </c>
-      <c r="Z22" s="6">
-        <f>groupSchedule!X1</f>
-        <v>0</v>
-      </c>
-      <c r="AA22" s="6">
-        <f>groupSchedule!Y1</f>
-        <v>0</v>
-      </c>
-      <c r="AB22" s="6">
-        <f>groupSchedule!Z1</f>
-        <v>0</v>
-      </c>
-      <c r="AC22" s="6">
-        <f>groupSchedule!AA1</f>
-        <v>0</v>
-      </c>
-      <c r="AD22" s="6">
-        <f>groupSchedule!AB1</f>
-        <v>0</v>
-      </c>
-      <c r="AE22" s="6">
-        <f>groupSchedule!AC1</f>
-        <v>0</v>
-      </c>
-      <c r="AF22" s="6">
-        <f>groupSchedule!AD1</f>
-        <v>0</v>
-      </c>
-      <c r="AG22" s="6">
-        <f>groupSchedule!AE1</f>
-        <v>0</v>
-      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6"/>
+      <c r="Y22" s="6"/>
+      <c r="Z22" s="6"/>
+      <c r="AA22" s="6"/>
+      <c r="AB22" s="6"/>
+      <c r="AC22" s="6"/>
+      <c r="AD22" s="6"/>
+      <c r="AE22" s="6"/>
+      <c r="AF22" s="6"/>
+      <c r="AG22" s="6"/>
       <c r="AI22" s="6"/>
       <c r="AJ22" s="10"/>
       <c r="AK22" s="2"/>
@@ -7588,130 +7494,37 @@
       <c r="B23" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="6">
-        <f>groupSchedule!A2</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="6">
-        <f>groupSchedule!B2</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="6">
-        <f>groupSchedule!C2</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="6">
-        <f>groupSchedule!D2</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="6">
-        <f>groupSchedule!E2</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="6">
-        <f>groupSchedule!F2</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="6">
-        <f>groupSchedule!G2</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="6">
-        <f>groupSchedule!H2</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="6">
-        <f>groupSchedule!I2</f>
-        <v>0</v>
-      </c>
-      <c r="L23" s="6">
-        <f>groupSchedule!J2</f>
-        <v>0</v>
-      </c>
-      <c r="M23" s="6">
-        <f>groupSchedule!K2</f>
-        <v>0</v>
-      </c>
-      <c r="N23" s="6">
-        <f>groupSchedule!L2</f>
-        <v>0</v>
-      </c>
-      <c r="O23" s="6">
-        <f>groupSchedule!M2</f>
-        <v>0</v>
-      </c>
-      <c r="P23" s="6">
-        <f>groupSchedule!N2</f>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="6">
-        <f>groupSchedule!O2</f>
-        <v>0</v>
-      </c>
-      <c r="R23" s="6">
-        <f>groupSchedule!P2</f>
-        <v>0</v>
-      </c>
-      <c r="S23" s="6">
-        <f>groupSchedule!Q2</f>
-        <v>0</v>
-      </c>
-      <c r="T23" s="6">
-        <f>groupSchedule!R2</f>
-        <v>0</v>
-      </c>
-      <c r="U23" s="6">
-        <f>groupSchedule!S2</f>
-        <v>0</v>
-      </c>
-      <c r="V23" s="6">
-        <f>groupSchedule!T2</f>
-        <v>0</v>
-      </c>
-      <c r="W23" s="6">
-        <f>groupSchedule!U2</f>
-        <v>0</v>
-      </c>
-      <c r="X23" s="6">
-        <f>groupSchedule!V2</f>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="6">
-        <f>groupSchedule!W2</f>
-        <v>0</v>
-      </c>
-      <c r="Z23" s="6">
-        <f>groupSchedule!X2</f>
-        <v>0</v>
-      </c>
-      <c r="AA23" s="6">
-        <f>groupSchedule!Y2</f>
-        <v>0</v>
-      </c>
-      <c r="AB23" s="6">
-        <f>groupSchedule!Z2</f>
-        <v>0</v>
-      </c>
-      <c r="AC23" s="6">
-        <f>groupSchedule!AA2</f>
-        <v>0</v>
-      </c>
-      <c r="AD23" s="6">
-        <f>groupSchedule!AB2</f>
-        <v>0</v>
-      </c>
-      <c r="AE23" s="6">
-        <f>groupSchedule!AC2</f>
-        <v>0</v>
-      </c>
-      <c r="AF23" s="6">
-        <f>groupSchedule!AD2</f>
-        <v>0</v>
-      </c>
-      <c r="AG23" s="6">
-        <f>groupSchedule!AE2</f>
-        <v>0</v>
-      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="6"/>
+      <c r="V23" s="6"/>
+      <c r="W23" s="6"/>
+      <c r="X23" s="6"/>
+      <c r="Y23" s="6"/>
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="6"/>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="6"/>
+      <c r="AD23" s="6"/>
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="6"/>
+      <c r="AG23" s="6"/>
       <c r="AI23" s="12"/>
       <c r="AJ23" s="10"/>
       <c r="AK23" s="2"/>
@@ -7731,130 +7544,37 @@
       <c r="B24" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="6">
-        <f>groupSchedule!A3</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="6">
-        <f>groupSchedule!B3</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="6">
-        <f>groupSchedule!C3</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="6">
-        <f>groupSchedule!D3</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="6">
-        <f>groupSchedule!E3</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="6">
-        <f>groupSchedule!F3</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="6">
-        <f>groupSchedule!G3</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="6">
-        <f>groupSchedule!H3</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="6">
-        <f>groupSchedule!I3</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="6">
-        <f>groupSchedule!J3</f>
-        <v>0</v>
-      </c>
-      <c r="M24" s="6">
-        <f>groupSchedule!K3</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="6">
-        <f>groupSchedule!L3</f>
-        <v>0</v>
-      </c>
-      <c r="O24" s="6">
-        <f>groupSchedule!M3</f>
-        <v>0</v>
-      </c>
-      <c r="P24" s="6">
-        <f>groupSchedule!N3</f>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="6">
-        <f>groupSchedule!O3</f>
-        <v>0</v>
-      </c>
-      <c r="R24" s="6">
-        <f>groupSchedule!P3</f>
-        <v>0</v>
-      </c>
-      <c r="S24" s="6">
-        <f>groupSchedule!Q3</f>
-        <v>0</v>
-      </c>
-      <c r="T24" s="6">
-        <f>groupSchedule!R3</f>
-        <v>0</v>
-      </c>
-      <c r="U24" s="6">
-        <f>groupSchedule!S3</f>
-        <v>0</v>
-      </c>
-      <c r="V24" s="6">
-        <f>groupSchedule!T3</f>
-        <v>0</v>
-      </c>
-      <c r="W24" s="6">
-        <f>groupSchedule!U3</f>
-        <v>0</v>
-      </c>
-      <c r="X24" s="6">
-        <f>groupSchedule!V3</f>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="6">
-        <f>groupSchedule!W3</f>
-        <v>0</v>
-      </c>
-      <c r="Z24" s="6">
-        <f>groupSchedule!X3</f>
-        <v>0</v>
-      </c>
-      <c r="AA24" s="6">
-        <f>groupSchedule!Y3</f>
-        <v>0</v>
-      </c>
-      <c r="AB24" s="6">
-        <f>groupSchedule!Z3</f>
-        <v>0</v>
-      </c>
-      <c r="AC24" s="6">
-        <f>groupSchedule!AA3</f>
-        <v>0</v>
-      </c>
-      <c r="AD24" s="6">
-        <f>groupSchedule!AB3</f>
-        <v>0</v>
-      </c>
-      <c r="AE24" s="6">
-        <f>groupSchedule!AC3</f>
-        <v>0</v>
-      </c>
-      <c r="AF24" s="6">
-        <f>groupSchedule!AD3</f>
-        <v>0</v>
-      </c>
-      <c r="AG24" s="6">
-        <f>groupSchedule!AE3</f>
-        <v>0</v>
-      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="6"/>
+      <c r="V24" s="6"/>
+      <c r="W24" s="6"/>
+      <c r="X24" s="6"/>
+      <c r="Y24" s="6"/>
+      <c r="Z24" s="6"/>
+      <c r="AA24" s="6"/>
+      <c r="AB24" s="6"/>
+      <c r="AC24" s="6"/>
+      <c r="AD24" s="6"/>
+      <c r="AE24" s="6"/>
+      <c r="AF24" s="6"/>
+      <c r="AG24" s="6"/>
       <c r="AI24" s="23"/>
       <c r="AJ24" s="24"/>
       <c r="AK24" s="2"/>
@@ -7874,130 +7594,37 @@
       <c r="B25" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="6">
-        <f>groupSchedule!A4</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="6">
-        <f>groupSchedule!B4</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="6">
-        <f>groupSchedule!C4</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="6">
-        <f>groupSchedule!D4</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="6">
-        <f>groupSchedule!E4</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="6">
-        <f>groupSchedule!F4</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="6">
-        <f>groupSchedule!G4</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="6">
-        <f>groupSchedule!H4</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="6">
-        <f>groupSchedule!I4</f>
-        <v>0</v>
-      </c>
-      <c r="L25" s="6">
-        <f>groupSchedule!J4</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="6">
-        <f>groupSchedule!K4</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="6">
-        <f>groupSchedule!L4</f>
-        <v>0</v>
-      </c>
-      <c r="O25" s="6">
-        <f>groupSchedule!M4</f>
-        <v>0</v>
-      </c>
-      <c r="P25" s="6">
-        <f>groupSchedule!N4</f>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="6">
-        <f>groupSchedule!O4</f>
-        <v>0</v>
-      </c>
-      <c r="R25" s="6">
-        <f>groupSchedule!P4</f>
-        <v>0</v>
-      </c>
-      <c r="S25" s="6">
-        <f>groupSchedule!Q4</f>
-        <v>0</v>
-      </c>
-      <c r="T25" s="6">
-        <f>groupSchedule!R4</f>
-        <v>0</v>
-      </c>
-      <c r="U25" s="6">
-        <f>groupSchedule!S4</f>
-        <v>0</v>
-      </c>
-      <c r="V25" s="6">
-        <f>groupSchedule!T4</f>
-        <v>0</v>
-      </c>
-      <c r="W25" s="6">
-        <f>groupSchedule!U4</f>
-        <v>0</v>
-      </c>
-      <c r="X25" s="6">
-        <f>groupSchedule!V4</f>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="6">
-        <f>groupSchedule!W4</f>
-        <v>0</v>
-      </c>
-      <c r="Z25" s="6">
-        <f>groupSchedule!X4</f>
-        <v>0</v>
-      </c>
-      <c r="AA25" s="6">
-        <f>groupSchedule!Y4</f>
-        <v>0</v>
-      </c>
-      <c r="AB25" s="6">
-        <f>groupSchedule!Z4</f>
-        <v>0</v>
-      </c>
-      <c r="AC25" s="6">
-        <f>groupSchedule!AA4</f>
-        <v>0</v>
-      </c>
-      <c r="AD25" s="6">
-        <f>groupSchedule!AB4</f>
-        <v>0</v>
-      </c>
-      <c r="AE25" s="6">
-        <f>groupSchedule!AC4</f>
-        <v>0</v>
-      </c>
-      <c r="AF25" s="6">
-        <f>groupSchedule!AD4</f>
-        <v>0</v>
-      </c>
-      <c r="AG25" s="6">
-        <f>groupSchedule!AE4</f>
-        <v>0</v>
-      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6"/>
+      <c r="U25" s="6"/>
+      <c r="V25" s="6"/>
+      <c r="W25" s="6"/>
+      <c r="X25" s="6"/>
+      <c r="Y25" s="6"/>
+      <c r="Z25" s="6"/>
+      <c r="AA25" s="6"/>
+      <c r="AB25" s="6"/>
+      <c r="AC25" s="6"/>
+      <c r="AD25" s="6"/>
+      <c r="AE25" s="6"/>
+      <c r="AF25" s="6"/>
+      <c r="AG25" s="6"/>
       <c r="AI25" s="26" t="s">
         <v>9</v>
       </c>
@@ -8167,7 +7794,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="12">
-        <f t="shared" ref="C27:AF27" si="11">COUNTIF(C6:C21,"야")</f>
+        <f t="shared" ref="C27:AG27" si="11">COUNTIF(C6:C21,"야")</f>
         <v>0</v>
       </c>
       <c r="D27" s="12">
@@ -8287,7 +7914,8 @@
         <v>0</v>
       </c>
       <c r="AG27" s="12">
-        <v>2</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="AH27" s="12"/>
       <c r="AI27" s="30">
@@ -8359,28 +7987,28 @@
     </row>
     <row r="29" spans="1:48">
       <c r="A29" s="36"/>
-      <c r="B29" s="88" t="s">
+      <c r="B29" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="89"/>
-      <c r="H29" s="89"/>
-      <c r="I29" s="89"/>
-      <c r="J29" s="89"/>
-      <c r="K29" s="89"/>
-      <c r="L29" s="89"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="91"/>
-      <c r="O29" s="92"/>
-      <c r="P29" s="92"/>
-      <c r="Q29" s="92"/>
-      <c r="R29" s="92"/>
-      <c r="S29" s="92"/>
-      <c r="T29" s="92"/>
-      <c r="U29" s="93"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="92"/>
+      <c r="F29" s="92"/>
+      <c r="G29" s="92"/>
+      <c r="H29" s="92"/>
+      <c r="I29" s="92"/>
+      <c r="J29" s="92"/>
+      <c r="K29" s="92"/>
+      <c r="L29" s="92"/>
+      <c r="M29" s="93"/>
+      <c r="N29" s="94"/>
+      <c r="O29" s="95"/>
+      <c r="P29" s="95"/>
+      <c r="Q29" s="95"/>
+      <c r="R29" s="95"/>
+      <c r="S29" s="95"/>
+      <c r="T29" s="95"/>
+      <c r="U29" s="96"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
@@ -8413,28 +8041,28 @@
     </row>
     <row r="30" spans="1:48">
       <c r="A30" s="1"/>
-      <c r="B30" s="94" t="s">
+      <c r="B30" s="97" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="95"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
-      <c r="F30" s="95"/>
-      <c r="G30" s="95"/>
-      <c r="H30" s="95"/>
-      <c r="I30" s="95"/>
-      <c r="J30" s="95"/>
-      <c r="K30" s="95"/>
-      <c r="L30" s="95"/>
-      <c r="M30" s="96"/>
-      <c r="N30" s="97"/>
-      <c r="O30" s="98"/>
-      <c r="P30" s="98"/>
-      <c r="Q30" s="98"/>
-      <c r="R30" s="98"/>
-      <c r="S30" s="98"/>
-      <c r="T30" s="98"/>
-      <c r="U30" s="99"/>
+      <c r="C30" s="98"/>
+      <c r="D30" s="98"/>
+      <c r="E30" s="98"/>
+      <c r="F30" s="98"/>
+      <c r="G30" s="98"/>
+      <c r="H30" s="98"/>
+      <c r="I30" s="98"/>
+      <c r="J30" s="98"/>
+      <c r="K30" s="98"/>
+      <c r="L30" s="98"/>
+      <c r="M30" s="99"/>
+      <c r="N30" s="100"/>
+      <c r="O30" s="101"/>
+      <c r="P30" s="101"/>
+      <c r="Q30" s="101"/>
+      <c r="R30" s="101"/>
+      <c r="S30" s="101"/>
+      <c r="T30" s="101"/>
+      <c r="U30" s="102"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
@@ -8466,28 +8094,28 @@
     </row>
     <row r="31" spans="1:48">
       <c r="A31" s="1"/>
-      <c r="B31" s="94" t="s">
+      <c r="B31" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="95"/>
-      <c r="D31" s="95"/>
-      <c r="E31" s="95"/>
-      <c r="F31" s="95"/>
-      <c r="G31" s="95"/>
-      <c r="H31" s="95"/>
-      <c r="I31" s="95"/>
-      <c r="J31" s="95"/>
-      <c r="K31" s="95"/>
-      <c r="L31" s="95"/>
-      <c r="M31" s="96"/>
-      <c r="N31" s="97"/>
-      <c r="O31" s="98"/>
-      <c r="P31" s="98"/>
-      <c r="Q31" s="98"/>
-      <c r="R31" s="98"/>
-      <c r="S31" s="98"/>
-      <c r="T31" s="98"/>
-      <c r="U31" s="99"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="98"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="98"/>
+      <c r="H31" s="98"/>
+      <c r="I31" s="98"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="98"/>
+      <c r="L31" s="98"/>
+      <c r="M31" s="99"/>
+      <c r="N31" s="100"/>
+      <c r="O31" s="101"/>
+      <c r="P31" s="101"/>
+      <c r="Q31" s="101"/>
+      <c r="R31" s="101"/>
+      <c r="S31" s="101"/>
+      <c r="T31" s="101"/>
+      <c r="U31" s="102"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
@@ -8523,28 +8151,28 @@
     </row>
     <row r="32" spans="1:48">
       <c r="A32" s="1"/>
-      <c r="B32" s="103" t="s">
+      <c r="B32" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="104"/>
-      <c r="D32" s="104"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="104"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="104"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="105"/>
-      <c r="N32" s="100"/>
-      <c r="O32" s="101"/>
-      <c r="P32" s="101"/>
-      <c r="Q32" s="101"/>
-      <c r="R32" s="101"/>
-      <c r="S32" s="101"/>
-      <c r="T32" s="101"/>
-      <c r="U32" s="102"/>
+      <c r="C32" s="107"/>
+      <c r="D32" s="107"/>
+      <c r="E32" s="107"/>
+      <c r="F32" s="107"/>
+      <c r="G32" s="107"/>
+      <c r="H32" s="107"/>
+      <c r="I32" s="107"/>
+      <c r="J32" s="107"/>
+      <c r="K32" s="107"/>
+      <c r="L32" s="107"/>
+      <c r="M32" s="108"/>
+      <c r="N32" s="103"/>
+      <c r="O32" s="104"/>
+      <c r="P32" s="104"/>
+      <c r="Q32" s="104"/>
+      <c r="R32" s="104"/>
+      <c r="S32" s="104"/>
+      <c r="T32" s="104"/>
+      <c r="U32" s="105"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
@@ -8577,18 +8205,18 @@
     </row>
     <row r="33" spans="1:40" ht="17.100000000000001" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="82"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="82"/>
-      <c r="H33" s="82"/>
-      <c r="I33" s="82"/>
-      <c r="J33" s="82"/>
-      <c r="K33" s="82"/>
-      <c r="L33" s="82"/>
-      <c r="M33" s="82"/>
+      <c r="B33" s="86"/>
+      <c r="C33" s="86"/>
+      <c r="D33" s="86"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="86"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="86"/>
       <c r="N33" s="45"/>
       <c r="O33" s="45"/>
       <c r="P33" s="45"/>
@@ -8621,18 +8249,18 @@
     </row>
     <row r="34" spans="1:40">
       <c r="A34" s="1"/>
-      <c r="B34" s="83"/>
-      <c r="C34" s="83"/>
-      <c r="D34" s="83"/>
-      <c r="E34" s="83"/>
-      <c r="F34" s="83"/>
-      <c r="G34" s="83"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="83"/>
-      <c r="J34" s="83"/>
-      <c r="K34" s="83"/>
-      <c r="L34" s="83"/>
-      <c r="M34" s="83"/>
+      <c r="B34" s="87"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="87"/>
+      <c r="E34" s="87"/>
+      <c r="F34" s="87"/>
+      <c r="G34" s="87"/>
+      <c r="H34" s="87"/>
+      <c r="I34" s="87"/>
+      <c r="J34" s="87"/>
+      <c r="K34" s="87"/>
+      <c r="L34" s="87"/>
+      <c r="M34" s="87"/>
       <c r="N34" s="46"/>
       <c r="O34" s="46"/>
       <c r="P34" s="46"/>
@@ -8668,18 +8296,18 @@
     </row>
     <row r="35" spans="1:40">
       <c r="A35" s="1"/>
-      <c r="B35" s="84"/>
-      <c r="C35" s="84"/>
-      <c r="D35" s="84"/>
-      <c r="E35" s="84"/>
-      <c r="F35" s="84"/>
-      <c r="G35" s="84"/>
-      <c r="H35" s="84"/>
-      <c r="I35" s="84"/>
-      <c r="J35" s="84"/>
-      <c r="K35" s="84"/>
-      <c r="L35" s="84"/>
-      <c r="M35" s="84"/>
+      <c r="B35" s="88"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="88"/>
+      <c r="E35" s="88"/>
+      <c r="F35" s="88"/>
+      <c r="G35" s="88"/>
+      <c r="H35" s="88"/>
+      <c r="I35" s="88"/>
+      <c r="J35" s="88"/>
+      <c r="K35" s="88"/>
+      <c r="L35" s="88"/>
+      <c r="M35" s="88"/>
       <c r="N35" s="46"/>
       <c r="O35" s="46"/>
       <c r="P35" s="46"/>
@@ -8797,11 +8425,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:AG2"/>
-    <mergeCell ref="A3:AG3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="AK4:AK5"/>
     <mergeCell ref="B33:M33"/>
     <mergeCell ref="B34:M34"/>
     <mergeCell ref="B35:M35"/>
@@ -8813,6 +8436,11 @@
     <mergeCell ref="N30:U32"/>
     <mergeCell ref="B31:M31"/>
     <mergeCell ref="B32:M32"/>
+    <mergeCell ref="A1:AG2"/>
+    <mergeCell ref="A3:AG3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="AK4:AK5"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="B6">
@@ -11154,51 +10782,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="111" t="str">
+      <c r="A2" s="136" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="112" t="s">
+      <c r="Q2" s="137" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114" t="s">
+      <c r="B3" s="139"/>
+      <c r="C3" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="113" t="s">
+      <c r="D3" s="139"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114" t="s">
+      <c r="G3" s="139"/>
+      <c r="H3" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="114"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="113" t="s">
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114" t="s">
+      <c r="L3" s="139"/>
+      <c r="M3" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="115"/>
+      <c r="N3" s="140"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -11210,10 +10838,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="116" t="s">
+      <c r="S3" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="117"/>
+      <c r="T3" s="142"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -11235,10 +10863,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="118" t="s">
+      <c r="R4" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="119"/>
+      <c r="S4" s="144"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -11264,8 +10892,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="121"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="146"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -11288,10 +10916,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="122" t="s">
+      <c r="R6" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="123"/>
+      <c r="S6" s="148"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -11314,10 +10942,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="124" t="s">
+      <c r="R7" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="125"/>
+      <c r="S7" s="150"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -11341,11 +10969,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="126" t="s">
+      <c r="R8" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="127"/>
-      <c r="T8" s="128"/>
+      <c r="S8" s="152"/>
+      <c r="T8" s="153"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -11367,10 +10995,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="109" t="s">
+      <c r="R9" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="110"/>
+      <c r="S9" s="135"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -11393,10 +11021,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="129" t="s">
+      <c r="R10" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="130"/>
+      <c r="S10" s="131"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -11422,8 +11050,8 @@
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="131"/>
-      <c r="T11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="118"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -11449,281 +11077,228 @@
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="134"/>
+      <c r="T12" s="112"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="135" t="s">
+      <c r="A13" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="137"/>
-      <c r="Q13" s="137"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="129"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="136"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="138"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="127"/>
+      <c r="Q14" s="127"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="139"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="139"/>
-      <c r="L15" s="139"/>
-      <c r="M15" s="139"/>
-      <c r="N15" s="139"/>
-      <c r="O15" s="139"/>
-      <c r="P15" s="139"/>
-      <c r="Q15" s="139"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="139"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="125"/>
+      <c r="T15" s="125"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="120"/>
+      <c r="C16" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135" t="s">
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="142" t="s">
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="142"/>
-      <c r="Q16" s="142"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="144" t="s">
+      <c r="P16" s="122"/>
+      <c r="Q16" s="122"/>
+      <c r="R16" s="123"/>
+      <c r="S16" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="144"/>
+      <c r="T16" s="124"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="136"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="143" t="s">
+      <c r="A17" s="121"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="144"/>
-      <c r="Q17" s="144" t="s">
+      <c r="P17" s="124"/>
+      <c r="Q17" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="144"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
+      <c r="T17" s="124"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="148"/>
-      <c r="M18" s="148"/>
-      <c r="N18" s="148"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="149"/>
-      <c r="R18" s="149"/>
-      <c r="S18" s="149"/>
-      <c r="T18" s="149"/>
+      <c r="A18" s="115"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="119"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="145"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="145"/>
-      <c r="K19" s="145"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="145"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="145"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="145"/>
-      <c r="S19" s="145"/>
-      <c r="T19" s="145"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="110"/>
+      <c r="T19" s="110"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="145"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="145"/>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="145"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="145"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="145"/>
-      <c r="S20" s="145"/>
-      <c r="T20" s="145"/>
+      <c r="A20" s="110"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="110"/>
+      <c r="T20" s="110"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="151"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="151"/>
-      <c r="I21" s="151"/>
-      <c r="J21" s="151"/>
-      <c r="K21" s="151"/>
-      <c r="L21" s="151"/>
-      <c r="M21" s="151"/>
-      <c r="N21" s="151"/>
-      <c r="O21" s="153"/>
-      <c r="P21" s="151"/>
-      <c r="Q21" s="151"/>
-      <c r="R21" s="151"/>
-      <c r="S21" s="151"/>
-      <c r="T21" s="151"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -11739,6 +11314,59 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="B11:O11">
@@ -12121,51 +11749,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="111" t="str">
+      <c r="A2" s="136" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="112" t="s">
+      <c r="Q2" s="137" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114" t="s">
+      <c r="B3" s="139"/>
+      <c r="C3" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="113" t="s">
+      <c r="D3" s="139"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114" t="s">
+      <c r="G3" s="139"/>
+      <c r="H3" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="114"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="113" t="s">
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114" t="s">
+      <c r="L3" s="139"/>
+      <c r="M3" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="115"/>
+      <c r="N3" s="140"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -12177,10 +11805,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="116" t="s">
+      <c r="S3" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="117"/>
+      <c r="T3" s="142"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -12202,10 +11830,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="118" t="s">
+      <c r="R4" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="119"/>
+      <c r="S4" s="144"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -12231,8 +11859,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="121"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="146"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -12255,10 +11883,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="122" t="s">
+      <c r="R6" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="123"/>
+      <c r="S6" s="148"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -12281,10 +11909,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="124" t="s">
+      <c r="R7" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="125"/>
+      <c r="S7" s="150"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -12308,11 +11936,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="126" t="s">
+      <c r="R8" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="127"/>
-      <c r="T8" s="128"/>
+      <c r="S8" s="152"/>
+      <c r="T8" s="153"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -12334,10 +11962,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="109" t="s">
+      <c r="R9" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="110"/>
+      <c r="S9" s="135"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -12360,10 +11988,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="129" t="s">
+      <c r="R10" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="130"/>
+      <c r="S10" s="131"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -12389,8 +12017,8 @@
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="131"/>
-      <c r="T11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="118"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -12416,281 +12044,228 @@
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="134"/>
+      <c r="T12" s="112"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="135" t="s">
+      <c r="A13" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="137"/>
-      <c r="Q13" s="137"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="129"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="136"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="138"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="127"/>
+      <c r="Q14" s="127"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="139"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="139"/>
-      <c r="L15" s="139"/>
-      <c r="M15" s="139"/>
-      <c r="N15" s="139"/>
-      <c r="O15" s="139"/>
-      <c r="P15" s="139"/>
-      <c r="Q15" s="139"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="139"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="125"/>
+      <c r="T15" s="125"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="120"/>
+      <c r="C16" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135" t="s">
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="142" t="s">
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="142"/>
-      <c r="Q16" s="142"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="144" t="s">
+      <c r="P16" s="122"/>
+      <c r="Q16" s="122"/>
+      <c r="R16" s="123"/>
+      <c r="S16" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="144"/>
+      <c r="T16" s="124"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="136"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="143" t="s">
+      <c r="A17" s="121"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="144"/>
-      <c r="Q17" s="144" t="s">
+      <c r="P17" s="124"/>
+      <c r="Q17" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="144"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
+      <c r="T17" s="124"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="148"/>
-      <c r="M18" s="148"/>
-      <c r="N18" s="148"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="149"/>
-      <c r="R18" s="149"/>
-      <c r="S18" s="149"/>
-      <c r="T18" s="149"/>
+      <c r="A18" s="115"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="119"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="145"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="145"/>
-      <c r="K19" s="145"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="145"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="145"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="145"/>
-      <c r="S19" s="145"/>
-      <c r="T19" s="145"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="110"/>
+      <c r="T19" s="110"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="145"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="145"/>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="145"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="145"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="145"/>
-      <c r="S20" s="145"/>
-      <c r="T20" s="145"/>
+      <c r="A20" s="110"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="110"/>
+      <c r="T20" s="110"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="151"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="151"/>
-      <c r="I21" s="151"/>
-      <c r="J21" s="151"/>
-      <c r="K21" s="151"/>
-      <c r="L21" s="151"/>
-      <c r="M21" s="151"/>
-      <c r="N21" s="151"/>
-      <c r="O21" s="153"/>
-      <c r="P21" s="151"/>
-      <c r="Q21" s="151"/>
-      <c r="R21" s="151"/>
-      <c r="S21" s="151"/>
-      <c r="T21" s="151"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -12706,6 +12281,59 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="B11:O11">
@@ -13088,51 +12716,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="111" t="str">
+      <c r="A2" s="136" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="112" t="s">
+      <c r="Q2" s="137" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114" t="s">
+      <c r="B3" s="139"/>
+      <c r="C3" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="113" t="s">
+      <c r="D3" s="139"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114" t="s">
+      <c r="G3" s="139"/>
+      <c r="H3" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="114"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="113" t="s">
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114" t="s">
+      <c r="L3" s="139"/>
+      <c r="M3" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="115"/>
+      <c r="N3" s="140"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -13144,10 +12772,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="116" t="s">
+      <c r="S3" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="117"/>
+      <c r="T3" s="142"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -13169,8 +12797,8 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="118"/>
-      <c r="S4" s="119"/>
+      <c r="R4" s="143"/>
+      <c r="S4" s="144"/>
       <c r="T4" s="73"/>
       <c r="V4" s="72"/>
     </row>
@@ -13194,8 +12822,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="121"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="146"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -13218,8 +12846,8 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="122"/>
-      <c r="S6" s="123"/>
+      <c r="R6" s="147"/>
+      <c r="S6" s="148"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -13242,8 +12870,8 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="124"/>
-      <c r="S7" s="125"/>
+      <c r="R7" s="149"/>
+      <c r="S7" s="150"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -13267,9 +12895,9 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="126"/>
-      <c r="S8" s="127"/>
-      <c r="T8" s="128"/>
+      <c r="R8" s="151"/>
+      <c r="S8" s="152"/>
+      <c r="T8" s="153"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -13291,8 +12919,8 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="109"/>
-      <c r="S9" s="110"/>
+      <c r="R9" s="134"/>
+      <c r="S9" s="135"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -13315,8 +12943,8 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="129"/>
-      <c r="S10" s="130"/>
+      <c r="R10" s="130"/>
+      <c r="S10" s="131"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -13340,8 +12968,8 @@
       <c r="P11" s="60"/>
       <c r="Q11" s="60"/>
       <c r="R11" s="62"/>
-      <c r="S11" s="131"/>
-      <c r="T11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="118"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -13365,279 +12993,226 @@
       <c r="Q12" s="60"/>
       <c r="R12" s="59"/>
       <c r="S12" s="133"/>
-      <c r="T12" s="134"/>
+      <c r="T12" s="112"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="135" t="s">
+      <c r="A13" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="137"/>
-      <c r="Q13" s="137"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
       <c r="R13" s="58"/>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="129"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="136"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="138"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="127"/>
+      <c r="Q14" s="127"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="139"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="139"/>
-      <c r="L15" s="139"/>
-      <c r="M15" s="139"/>
-      <c r="N15" s="139"/>
-      <c r="O15" s="139"/>
-      <c r="P15" s="139"/>
-      <c r="Q15" s="139"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="139"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="125"/>
+      <c r="T15" s="125"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="120"/>
+      <c r="C16" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135" t="s">
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="142" t="s">
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="142"/>
-      <c r="Q16" s="142"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="144" t="s">
+      <c r="P16" s="122"/>
+      <c r="Q16" s="122"/>
+      <c r="R16" s="123"/>
+      <c r="S16" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="144"/>
+      <c r="T16" s="124"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="136"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="143" t="s">
+      <c r="A17" s="121"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="144"/>
-      <c r="Q17" s="144" t="s">
+      <c r="P17" s="124"/>
+      <c r="Q17" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="144"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
+      <c r="T17" s="124"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="148"/>
-      <c r="M18" s="148"/>
-      <c r="N18" s="148"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="149"/>
-      <c r="R18" s="149"/>
-      <c r="S18" s="149"/>
-      <c r="T18" s="149"/>
+      <c r="A18" s="115"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="119"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="145"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="145"/>
-      <c r="K19" s="145"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="145"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="145"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="145"/>
-      <c r="S19" s="145"/>
-      <c r="T19" s="145"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="110"/>
+      <c r="T19" s="110"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="145"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="145"/>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="145"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="145"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="145"/>
-      <c r="S20" s="145"/>
-      <c r="T20" s="145"/>
+      <c r="A20" s="110"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="110"/>
+      <c r="T20" s="110"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="151"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="151"/>
-      <c r="I21" s="151"/>
-      <c r="J21" s="151"/>
-      <c r="K21" s="151"/>
-      <c r="L21" s="151"/>
-      <c r="M21" s="151"/>
-      <c r="N21" s="151"/>
-      <c r="O21" s="153"/>
-      <c r="P21" s="151"/>
-      <c r="Q21" s="151"/>
-      <c r="R21" s="151"/>
-      <c r="S21" s="151"/>
-      <c r="T21" s="151"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -13653,6 +13228,59 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="B11:O11">
@@ -14035,51 +13663,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="111" t="str">
+      <c r="A2" s="136" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="112" t="s">
+      <c r="Q2" s="137" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114" t="s">
+      <c r="B3" s="139"/>
+      <c r="C3" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="113" t="s">
+      <c r="D3" s="139"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114" t="s">
+      <c r="G3" s="139"/>
+      <c r="H3" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="114"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="113" t="s">
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114" t="s">
+      <c r="L3" s="139"/>
+      <c r="M3" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="115"/>
+      <c r="N3" s="140"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -14091,10 +13719,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="116" t="s">
+      <c r="S3" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="117"/>
+      <c r="T3" s="142"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -14116,10 +13744,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="118" t="s">
+      <c r="R4" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="119"/>
+      <c r="S4" s="144"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -14145,8 +13773,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="121"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="146"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -14169,10 +13797,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="122" t="s">
+      <c r="R6" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="123"/>
+      <c r="S6" s="148"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -14195,10 +13823,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="124" t="s">
+      <c r="R7" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="125"/>
+      <c r="S7" s="150"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -14222,11 +13850,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="126" t="s">
+      <c r="R8" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="127"/>
-      <c r="T8" s="128"/>
+      <c r="S8" s="152"/>
+      <c r="T8" s="153"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -14248,10 +13876,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="109" t="s">
+      <c r="R9" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="110"/>
+      <c r="S9" s="135"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -14274,10 +13902,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="129" t="s">
+      <c r="R10" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="130"/>
+      <c r="S10" s="131"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -14303,8 +13931,8 @@
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="131"/>
-      <c r="T11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="118"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -14330,281 +13958,228 @@
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="134"/>
+      <c r="T12" s="112"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="135" t="s">
+      <c r="A13" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="137"/>
-      <c r="Q13" s="137"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="129"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="136"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="138"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="127"/>
+      <c r="Q14" s="127"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="139"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="139"/>
-      <c r="L15" s="139"/>
-      <c r="M15" s="139"/>
-      <c r="N15" s="139"/>
-      <c r="O15" s="139"/>
-      <c r="P15" s="139"/>
-      <c r="Q15" s="139"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="139"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="125"/>
+      <c r="T15" s="125"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="120"/>
+      <c r="C16" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135" t="s">
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="142" t="s">
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="142"/>
-      <c r="Q16" s="142"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="144" t="s">
+      <c r="P16" s="122"/>
+      <c r="Q16" s="122"/>
+      <c r="R16" s="123"/>
+      <c r="S16" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="144"/>
+      <c r="T16" s="124"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="136"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="143" t="s">
+      <c r="A17" s="121"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="144"/>
-      <c r="Q17" s="144" t="s">
+      <c r="P17" s="124"/>
+      <c r="Q17" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="144"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
+      <c r="T17" s="124"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="148"/>
-      <c r="M18" s="148"/>
-      <c r="N18" s="148"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="149"/>
-      <c r="R18" s="149"/>
-      <c r="S18" s="149"/>
-      <c r="T18" s="149"/>
+      <c r="A18" s="115"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="119"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="145"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="145"/>
-      <c r="K19" s="145"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="145"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="145"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="145"/>
-      <c r="S19" s="145"/>
-      <c r="T19" s="145"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="110"/>
+      <c r="T19" s="110"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="145"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="145"/>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="145"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="145"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="145"/>
-      <c r="S20" s="145"/>
-      <c r="T20" s="145"/>
+      <c r="A20" s="110"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="110"/>
+      <c r="T20" s="110"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="151"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="151"/>
-      <c r="I21" s="151"/>
-      <c r="J21" s="151"/>
-      <c r="K21" s="151"/>
-      <c r="L21" s="151"/>
-      <c r="M21" s="151"/>
-      <c r="N21" s="151"/>
-      <c r="O21" s="153"/>
-      <c r="P21" s="151"/>
-      <c r="Q21" s="151"/>
-      <c r="R21" s="151"/>
-      <c r="S21" s="151"/>
-      <c r="T21" s="151"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -14620,6 +14195,59 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="B11:O11">
@@ -15002,51 +14630,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="111" t="str">
+      <c r="A2" s="136" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="112" t="s">
+      <c r="Q2" s="137" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114" t="s">
+      <c r="B3" s="139"/>
+      <c r="C3" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="113" t="s">
+      <c r="D3" s="139"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114" t="s">
+      <c r="G3" s="139"/>
+      <c r="H3" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="114"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="113" t="s">
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114" t="s">
+      <c r="L3" s="139"/>
+      <c r="M3" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="115"/>
+      <c r="N3" s="140"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -15058,10 +14686,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="116" t="s">
+      <c r="S3" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="117"/>
+      <c r="T3" s="142"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -15083,10 +14711,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="118" t="s">
+      <c r="R4" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="119"/>
+      <c r="S4" s="144"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -15112,8 +14740,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="121"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="146"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -15136,10 +14764,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="122" t="s">
+      <c r="R6" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="123"/>
+      <c r="S6" s="148"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -15162,10 +14790,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="124" t="s">
+      <c r="R7" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="125"/>
+      <c r="S7" s="150"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -15189,11 +14817,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="126" t="s">
+      <c r="R8" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="127"/>
-      <c r="T8" s="128"/>
+      <c r="S8" s="152"/>
+      <c r="T8" s="153"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -15215,10 +14843,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="109" t="s">
+      <c r="R9" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="110"/>
+      <c r="S9" s="135"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -15241,10 +14869,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="129" t="s">
+      <c r="R10" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="130"/>
+      <c r="S10" s="131"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -15270,8 +14898,8 @@
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="131"/>
-      <c r="T11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="118"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -15297,281 +14925,228 @@
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="134"/>
+      <c r="T12" s="112"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="135" t="s">
+      <c r="A13" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="137"/>
-      <c r="Q13" s="137"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="129"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="136"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="138"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="127"/>
+      <c r="Q14" s="127"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="139"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="139"/>
-      <c r="L15" s="139"/>
-      <c r="M15" s="139"/>
-      <c r="N15" s="139"/>
-      <c r="O15" s="139"/>
-      <c r="P15" s="139"/>
-      <c r="Q15" s="139"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="139"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="125"/>
+      <c r="T15" s="125"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="120"/>
+      <c r="C16" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135" t="s">
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="142" t="s">
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="142"/>
-      <c r="Q16" s="142"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="144" t="s">
+      <c r="P16" s="122"/>
+      <c r="Q16" s="122"/>
+      <c r="R16" s="123"/>
+      <c r="S16" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="144"/>
+      <c r="T16" s="124"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="136"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="143" t="s">
+      <c r="A17" s="121"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="144"/>
-      <c r="Q17" s="144" t="s">
+      <c r="P17" s="124"/>
+      <c r="Q17" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="144"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
+      <c r="T17" s="124"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="148"/>
-      <c r="M18" s="148"/>
-      <c r="N18" s="148"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="149"/>
-      <c r="R18" s="149"/>
-      <c r="S18" s="149"/>
-      <c r="T18" s="149"/>
+      <c r="A18" s="115"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="119"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="145"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="145"/>
-      <c r="K19" s="145"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="145"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="145"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="145"/>
-      <c r="S19" s="145"/>
-      <c r="T19" s="145"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="110"/>
+      <c r="T19" s="110"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="145"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="145"/>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="145"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="145"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="145"/>
-      <c r="S20" s="145"/>
-      <c r="T20" s="145"/>
+      <c r="A20" s="110"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="110"/>
+      <c r="T20" s="110"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="151"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="151"/>
-      <c r="I21" s="151"/>
-      <c r="J21" s="151"/>
-      <c r="K21" s="151"/>
-      <c r="L21" s="151"/>
-      <c r="M21" s="151"/>
-      <c r="N21" s="151"/>
-      <c r="O21" s="153"/>
-      <c r="P21" s="151"/>
-      <c r="Q21" s="151"/>
-      <c r="R21" s="151"/>
-      <c r="S21" s="151"/>
-      <c r="T21" s="151"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -15587,6 +15162,59 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="B11:O11">
@@ -15969,51 +15597,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="111" t="str">
+      <c r="A2" s="136" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="112" t="s">
+      <c r="Q2" s="137" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114" t="s">
+      <c r="B3" s="139"/>
+      <c r="C3" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="113" t="s">
+      <c r="D3" s="139"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114" t="s">
+      <c r="G3" s="139"/>
+      <c r="H3" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="114"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="113" t="s">
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114" t="s">
+      <c r="L3" s="139"/>
+      <c r="M3" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="115"/>
+      <c r="N3" s="140"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -16025,10 +15653,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="116" t="s">
+      <c r="S3" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="117"/>
+      <c r="T3" s="142"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -16050,10 +15678,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="118" t="s">
+      <c r="R4" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="119"/>
+      <c r="S4" s="144"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -16079,8 +15707,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="121"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="146"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -16103,10 +15731,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="122" t="s">
+      <c r="R6" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="123"/>
+      <c r="S6" s="148"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -16129,10 +15757,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="124" t="s">
+      <c r="R7" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="125"/>
+      <c r="S7" s="150"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -16156,11 +15784,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="126" t="s">
+      <c r="R8" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="127"/>
-      <c r="T8" s="128"/>
+      <c r="S8" s="152"/>
+      <c r="T8" s="153"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -16182,10 +15810,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="109" t="s">
+      <c r="R9" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="110"/>
+      <c r="S9" s="135"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -16208,10 +15836,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="129" t="s">
+      <c r="R10" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="130"/>
+      <c r="S10" s="131"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -16237,8 +15865,8 @@
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="131"/>
-      <c r="T11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="118"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -16264,228 +15892,284 @@
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="134"/>
+      <c r="T12" s="112"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="135" t="s">
+      <c r="A13" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="137"/>
-      <c r="Q13" s="137"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="129"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="136"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="138"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="127"/>
+      <c r="Q14" s="127"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="139"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="139"/>
-      <c r="L15" s="139"/>
-      <c r="M15" s="139"/>
-      <c r="N15" s="139"/>
-      <c r="O15" s="139"/>
-      <c r="P15" s="139"/>
-      <c r="Q15" s="139"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="139"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="125"/>
+      <c r="T15" s="125"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="120"/>
+      <c r="C16" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135" t="s">
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="142" t="s">
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="142"/>
-      <c r="Q16" s="142"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="144" t="s">
+      <c r="P16" s="122"/>
+      <c r="Q16" s="122"/>
+      <c r="R16" s="123"/>
+      <c r="S16" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="144"/>
+      <c r="T16" s="124"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="136"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="143" t="s">
+      <c r="A17" s="121"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="144"/>
-      <c r="Q17" s="144" t="s">
+      <c r="P17" s="124"/>
+      <c r="Q17" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="144"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
+      <c r="T17" s="124"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="148"/>
-      <c r="M18" s="148"/>
-      <c r="N18" s="148"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="149"/>
-      <c r="R18" s="149"/>
-      <c r="S18" s="149"/>
-      <c r="T18" s="149"/>
+      <c r="A18" s="115"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="119"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="145"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="145"/>
-      <c r="K19" s="145"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="145"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="145"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="145"/>
-      <c r="S19" s="145"/>
-      <c r="T19" s="145"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="110"/>
+      <c r="T19" s="110"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="145"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="145"/>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="145"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="145"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="145"/>
-      <c r="S20" s="145"/>
-      <c r="T20" s="145"/>
+      <c r="A20" s="110"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="110"/>
+      <c r="T20" s="110"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="151"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="151"/>
-      <c r="I21" s="151"/>
-      <c r="J21" s="151"/>
-      <c r="K21" s="151"/>
-      <c r="L21" s="151"/>
-      <c r="M21" s="151"/>
-      <c r="N21" s="151"/>
-      <c r="O21" s="153"/>
-      <c r="P21" s="151"/>
-      <c r="Q21" s="151"/>
-      <c r="R21" s="151"/>
-      <c r="S21" s="151"/>
-      <c r="T21" s="151"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
     <mergeCell ref="S20:T20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="C21:G21"/>
@@ -16498,62 +16182,6 @@
     <mergeCell ref="H20:N20"/>
     <mergeCell ref="O20:P20"/>
     <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="S3:T3"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="B11:O11">
@@ -16697,7 +16325,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <sheetData/>
@@ -16708,7 +16336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <sheetData/>
@@ -16719,7 +16347,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <sheetData/>
@@ -16730,17 +16358,6 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
-  <sheetData/>
-  <phoneticPr fontId="19" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
@@ -17098,51 +16715,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="111" t="str">
+      <c r="A2" s="136" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="112" t="s">
+      <c r="Q2" s="137" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114" t="s">
+      <c r="B3" s="139"/>
+      <c r="C3" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="113" t="s">
+      <c r="D3" s="139"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114" t="s">
+      <c r="G3" s="139"/>
+      <c r="H3" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="114"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="113" t="s">
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114" t="s">
+      <c r="L3" s="139"/>
+      <c r="M3" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="115"/>
+      <c r="N3" s="140"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -17154,10 +16771,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="116" t="s">
+      <c r="S3" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="117"/>
+      <c r="T3" s="142"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -17179,10 +16796,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="118" t="s">
+      <c r="R4" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="119"/>
+      <c r="S4" s="144"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -17208,8 +16825,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="121"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="146"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -17232,10 +16849,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="122" t="s">
+      <c r="R6" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="123"/>
+      <c r="S6" s="148"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -17258,10 +16875,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="124" t="s">
+      <c r="R7" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="125"/>
+      <c r="S7" s="150"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -17285,11 +16902,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="126" t="s">
+      <c r="R8" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="127"/>
-      <c r="T8" s="128"/>
+      <c r="S8" s="152"/>
+      <c r="T8" s="153"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -17311,10 +16928,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="109" t="s">
+      <c r="R9" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="110"/>
+      <c r="S9" s="135"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -17337,10 +16954,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="129" t="s">
+      <c r="R10" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="130"/>
+      <c r="S10" s="131"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -17366,8 +16983,8 @@
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="131"/>
-      <c r="T11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="118"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -17393,281 +17010,228 @@
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="134"/>
+      <c r="T12" s="112"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="135" t="s">
+      <c r="A13" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="137"/>
-      <c r="Q13" s="137"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="129"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="136"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="138"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="127"/>
+      <c r="Q14" s="127"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="139"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="139"/>
-      <c r="L15" s="139"/>
-      <c r="M15" s="139"/>
-      <c r="N15" s="139"/>
-      <c r="O15" s="139"/>
-      <c r="P15" s="139"/>
-      <c r="Q15" s="139"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="139"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="125"/>
+      <c r="T15" s="125"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="120"/>
+      <c r="C16" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135" t="s">
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="142" t="s">
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="142"/>
-      <c r="Q16" s="142"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="144" t="s">
+      <c r="P16" s="122"/>
+      <c r="Q16" s="122"/>
+      <c r="R16" s="123"/>
+      <c r="S16" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="144"/>
+      <c r="T16" s="124"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="136"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="143" t="s">
+      <c r="A17" s="121"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="144"/>
-      <c r="Q17" s="144" t="s">
+      <c r="P17" s="124"/>
+      <c r="Q17" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="144"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
+      <c r="T17" s="124"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="148"/>
-      <c r="M18" s="148"/>
-      <c r="N18" s="148"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="149"/>
-      <c r="R18" s="149"/>
-      <c r="S18" s="149"/>
-      <c r="T18" s="149"/>
+      <c r="A18" s="115"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="119"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="145"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="145"/>
-      <c r="K19" s="145"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="145"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="145"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="145"/>
-      <c r="S19" s="145"/>
-      <c r="T19" s="145"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="110"/>
+      <c r="T19" s="110"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="145"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="145"/>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="145"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="145"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="145"/>
-      <c r="S20" s="145"/>
-      <c r="T20" s="145"/>
+      <c r="A20" s="110"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="110"/>
+      <c r="T20" s="110"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="151"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="151"/>
-      <c r="I21" s="151"/>
-      <c r="J21" s="151"/>
-      <c r="K21" s="151"/>
-      <c r="L21" s="151"/>
-      <c r="M21" s="151"/>
-      <c r="N21" s="151"/>
-      <c r="O21" s="153"/>
-      <c r="P21" s="151"/>
-      <c r="Q21" s="151"/>
-      <c r="R21" s="151"/>
-      <c r="S21" s="151"/>
-      <c r="T21" s="151"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -17683,6 +17247,59 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="B11:O11">
@@ -18065,51 +17682,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="111" t="str">
+      <c r="A2" s="136" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="112" t="s">
+      <c r="Q2" s="137" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114" t="s">
+      <c r="B3" s="139"/>
+      <c r="C3" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="113" t="s">
+      <c r="D3" s="139"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114" t="s">
+      <c r="G3" s="139"/>
+      <c r="H3" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="114"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="113" t="s">
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114" t="s">
+      <c r="L3" s="139"/>
+      <c r="M3" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="115"/>
+      <c r="N3" s="140"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -18121,10 +17738,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="116" t="s">
+      <c r="S3" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="117"/>
+      <c r="T3" s="142"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -18146,10 +17763,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="118" t="s">
+      <c r="R4" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="119"/>
+      <c r="S4" s="144"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -18175,8 +17792,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="121"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="146"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -18199,10 +17816,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="122" t="s">
+      <c r="R6" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="123"/>
+      <c r="S6" s="148"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -18225,10 +17842,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="124" t="s">
+      <c r="R7" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="125"/>
+      <c r="S7" s="150"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -18252,11 +17869,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="126" t="s">
+      <c r="R8" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="127"/>
-      <c r="T8" s="128"/>
+      <c r="S8" s="152"/>
+      <c r="T8" s="153"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -18278,10 +17895,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="109" t="s">
+      <c r="R9" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="110"/>
+      <c r="S9" s="135"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -18304,10 +17921,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="129" t="s">
+      <c r="R10" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="130"/>
+      <c r="S10" s="131"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -18333,8 +17950,8 @@
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="131"/>
-      <c r="T11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="118"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -18360,281 +17977,228 @@
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="134"/>
+      <c r="T12" s="112"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="135" t="s">
+      <c r="A13" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="137"/>
-      <c r="Q13" s="137"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="129"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="136"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="138"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="127"/>
+      <c r="Q14" s="127"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="139"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="139"/>
-      <c r="L15" s="139"/>
-      <c r="M15" s="139"/>
-      <c r="N15" s="139"/>
-      <c r="O15" s="139"/>
-      <c r="P15" s="139"/>
-      <c r="Q15" s="139"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="139"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="125"/>
+      <c r="T15" s="125"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="120"/>
+      <c r="C16" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135" t="s">
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="142" t="s">
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="142"/>
-      <c r="Q16" s="142"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="144" t="s">
+      <c r="P16" s="122"/>
+      <c r="Q16" s="122"/>
+      <c r="R16" s="123"/>
+      <c r="S16" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="144"/>
+      <c r="T16" s="124"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="136"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="143" t="s">
+      <c r="A17" s="121"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="144"/>
-      <c r="Q17" s="144" t="s">
+      <c r="P17" s="124"/>
+      <c r="Q17" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="144"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
+      <c r="T17" s="124"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="148"/>
-      <c r="M18" s="148"/>
-      <c r="N18" s="148"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="149"/>
-      <c r="R18" s="149"/>
-      <c r="S18" s="149"/>
-      <c r="T18" s="149"/>
+      <c r="A18" s="115"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="119"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="145"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="145"/>
-      <c r="K19" s="145"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="145"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="145"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="145"/>
-      <c r="S19" s="145"/>
-      <c r="T19" s="145"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="110"/>
+      <c r="T19" s="110"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="145"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="145"/>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="145"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="145"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="145"/>
-      <c r="S20" s="145"/>
-      <c r="T20" s="145"/>
+      <c r="A20" s="110"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="110"/>
+      <c r="T20" s="110"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="151"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="151"/>
-      <c r="I21" s="151"/>
-      <c r="J21" s="151"/>
-      <c r="K21" s="151"/>
-      <c r="L21" s="151"/>
-      <c r="M21" s="151"/>
-      <c r="N21" s="151"/>
-      <c r="O21" s="153"/>
-      <c r="P21" s="151"/>
-      <c r="Q21" s="151"/>
-      <c r="R21" s="151"/>
-      <c r="S21" s="151"/>
-      <c r="T21" s="151"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -18650,6 +18214,59 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="B11:O11">
@@ -19032,51 +18649,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="111" t="str">
+      <c r="A2" s="136" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="112" t="s">
+      <c r="Q2" s="137" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114" t="s">
+      <c r="B3" s="139"/>
+      <c r="C3" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="113" t="s">
+      <c r="D3" s="139"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114" t="s">
+      <c r="G3" s="139"/>
+      <c r="H3" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="114"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="113" t="s">
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114" t="s">
+      <c r="L3" s="139"/>
+      <c r="M3" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="115"/>
+      <c r="N3" s="140"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -19088,10 +18705,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="116" t="s">
+      <c r="S3" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="117"/>
+      <c r="T3" s="142"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -19113,10 +18730,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="118" t="s">
+      <c r="R4" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="119"/>
+      <c r="S4" s="144"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -19142,8 +18759,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="121"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="146"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -19166,10 +18783,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="122" t="s">
+      <c r="R6" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="123"/>
+      <c r="S6" s="148"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -19192,10 +18809,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="124" t="s">
+      <c r="R7" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="125"/>
+      <c r="S7" s="150"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -19219,11 +18836,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="126" t="s">
+      <c r="R8" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="127"/>
-      <c r="T8" s="128"/>
+      <c r="S8" s="152"/>
+      <c r="T8" s="153"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -19245,10 +18862,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="109" t="s">
+      <c r="R9" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="110"/>
+      <c r="S9" s="135"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -19271,10 +18888,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="129" t="s">
+      <c r="R10" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="130"/>
+      <c r="S10" s="131"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -19300,8 +18917,8 @@
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="131"/>
-      <c r="T11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="118"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -19327,281 +18944,228 @@
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="134"/>
+      <c r="T12" s="112"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="135" t="s">
+      <c r="A13" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="137"/>
-      <c r="Q13" s="137"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="129"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="136"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="138"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="127"/>
+      <c r="Q14" s="127"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="139"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="139"/>
-      <c r="L15" s="139"/>
-      <c r="M15" s="139"/>
-      <c r="N15" s="139"/>
-      <c r="O15" s="139"/>
-      <c r="P15" s="139"/>
-      <c r="Q15" s="139"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="139"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="125"/>
+      <c r="T15" s="125"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="120"/>
+      <c r="C16" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135" t="s">
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="142" t="s">
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="142"/>
-      <c r="Q16" s="142"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="144" t="s">
+      <c r="P16" s="122"/>
+      <c r="Q16" s="122"/>
+      <c r="R16" s="123"/>
+      <c r="S16" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="144"/>
+      <c r="T16" s="124"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="136"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="143" t="s">
+      <c r="A17" s="121"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="144"/>
-      <c r="Q17" s="144" t="s">
+      <c r="P17" s="124"/>
+      <c r="Q17" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="144"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
+      <c r="T17" s="124"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="148"/>
-      <c r="M18" s="148"/>
-      <c r="N18" s="148"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="149"/>
-      <c r="R18" s="149"/>
-      <c r="S18" s="149"/>
-      <c r="T18" s="149"/>
+      <c r="A18" s="115"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="119"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="145"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="145"/>
-      <c r="K19" s="145"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="145"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="145"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="145"/>
-      <c r="S19" s="145"/>
-      <c r="T19" s="145"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="110"/>
+      <c r="T19" s="110"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="145"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="145"/>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="145"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="145"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="145"/>
-      <c r="S20" s="145"/>
-      <c r="T20" s="145"/>
+      <c r="A20" s="110"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="110"/>
+      <c r="T20" s="110"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="151"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="151"/>
-      <c r="I21" s="151"/>
-      <c r="J21" s="151"/>
-      <c r="K21" s="151"/>
-      <c r="L21" s="151"/>
-      <c r="M21" s="151"/>
-      <c r="N21" s="151"/>
-      <c r="O21" s="153"/>
-      <c r="P21" s="151"/>
-      <c r="Q21" s="151"/>
-      <c r="R21" s="151"/>
-      <c r="S21" s="151"/>
-      <c r="T21" s="151"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -19617,6 +19181,59 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="B11:O11">
@@ -19999,51 +19616,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="111" t="str">
+      <c r="A2" s="136" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="112" t="s">
+      <c r="Q2" s="137" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114" t="s">
+      <c r="B3" s="139"/>
+      <c r="C3" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="113" t="s">
+      <c r="D3" s="139"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114" t="s">
+      <c r="G3" s="139"/>
+      <c r="H3" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="114"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="113" t="s">
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114" t="s">
+      <c r="L3" s="139"/>
+      <c r="M3" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="115"/>
+      <c r="N3" s="140"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -20055,10 +19672,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="116" t="s">
+      <c r="S3" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="117"/>
+      <c r="T3" s="142"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -20080,10 +19697,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="118" t="s">
+      <c r="R4" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="119"/>
+      <c r="S4" s="144"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -20109,8 +19726,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="121"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="146"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -20133,10 +19750,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="122" t="s">
+      <c r="R6" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="123"/>
+      <c r="S6" s="148"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -20159,10 +19776,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="124" t="s">
+      <c r="R7" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="125"/>
+      <c r="S7" s="150"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -20186,11 +19803,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="126" t="s">
+      <c r="R8" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="127"/>
-      <c r="T8" s="128"/>
+      <c r="S8" s="152"/>
+      <c r="T8" s="153"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -20212,10 +19829,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="109" t="s">
+      <c r="R9" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="110"/>
+      <c r="S9" s="135"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -20238,10 +19855,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="129" t="s">
+      <c r="R10" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="130"/>
+      <c r="S10" s="131"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -20267,8 +19884,8 @@
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="131"/>
-      <c r="T11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="118"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -20294,281 +19911,228 @@
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="134"/>
+      <c r="T12" s="112"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="135" t="s">
+      <c r="A13" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="137"/>
-      <c r="Q13" s="137"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="129"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="136"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="138"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="127"/>
+      <c r="Q14" s="127"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="139"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="139"/>
-      <c r="L15" s="139"/>
-      <c r="M15" s="139"/>
-      <c r="N15" s="139"/>
-      <c r="O15" s="139"/>
-      <c r="P15" s="139"/>
-      <c r="Q15" s="139"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="139"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="125"/>
+      <c r="T15" s="125"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="120"/>
+      <c r="C16" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135" t="s">
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="142" t="s">
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="142"/>
-      <c r="Q16" s="142"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="144" t="s">
+      <c r="P16" s="122"/>
+      <c r="Q16" s="122"/>
+      <c r="R16" s="123"/>
+      <c r="S16" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="144"/>
+      <c r="T16" s="124"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="136"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="143" t="s">
+      <c r="A17" s="121"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="144"/>
-      <c r="Q17" s="144" t="s">
+      <c r="P17" s="124"/>
+      <c r="Q17" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="144"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
+      <c r="T17" s="124"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="148"/>
-      <c r="M18" s="148"/>
-      <c r="N18" s="148"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="149"/>
-      <c r="R18" s="149"/>
-      <c r="S18" s="149"/>
-      <c r="T18" s="149"/>
+      <c r="A18" s="115"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="119"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="145"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="145"/>
-      <c r="K19" s="145"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="145"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="145"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="145"/>
-      <c r="S19" s="145"/>
-      <c r="T19" s="145"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="110"/>
+      <c r="T19" s="110"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="145"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="145"/>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="145"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="145"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="145"/>
-      <c r="S20" s="145"/>
-      <c r="T20" s="145"/>
+      <c r="A20" s="110"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="110"/>
+      <c r="T20" s="110"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="151"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="151"/>
-      <c r="I21" s="151"/>
-      <c r="J21" s="151"/>
-      <c r="K21" s="151"/>
-      <c r="L21" s="151"/>
-      <c r="M21" s="151"/>
-      <c r="N21" s="151"/>
-      <c r="O21" s="153"/>
-      <c r="P21" s="151"/>
-      <c r="Q21" s="151"/>
-      <c r="R21" s="151"/>
-      <c r="S21" s="151"/>
-      <c r="T21" s="151"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -20584,6 +20148,59 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="B11:O11">
@@ -20966,51 +20583,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="111" t="str">
+      <c r="A2" s="136" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="112" t="s">
+      <c r="Q2" s="137" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114" t="s">
+      <c r="B3" s="139"/>
+      <c r="C3" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="113" t="s">
+      <c r="D3" s="139"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114" t="s">
+      <c r="G3" s="139"/>
+      <c r="H3" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="114"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="113" t="s">
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114" t="s">
+      <c r="L3" s="139"/>
+      <c r="M3" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="115"/>
+      <c r="N3" s="140"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -21022,10 +20639,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="116" t="s">
+      <c r="S3" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="117"/>
+      <c r="T3" s="142"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -21047,10 +20664,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="118" t="s">
+      <c r="R4" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="119"/>
+      <c r="S4" s="144"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -21076,8 +20693,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="121"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="146"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -21100,10 +20717,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="122" t="s">
+      <c r="R6" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="123"/>
+      <c r="S6" s="148"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -21126,10 +20743,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="124" t="s">
+      <c r="R7" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="125"/>
+      <c r="S7" s="150"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -21153,11 +20770,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="126" t="s">
+      <c r="R8" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="127"/>
-      <c r="T8" s="128"/>
+      <c r="S8" s="152"/>
+      <c r="T8" s="153"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -21179,10 +20796,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="109" t="s">
+      <c r="R9" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="110"/>
+      <c r="S9" s="135"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -21205,10 +20822,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="129" t="s">
+      <c r="R10" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="130"/>
+      <c r="S10" s="131"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -21234,8 +20851,8 @@
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="131"/>
-      <c r="T11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="118"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -21261,281 +20878,228 @@
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="134"/>
+      <c r="T12" s="112"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="135" t="s">
+      <c r="A13" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="137"/>
-      <c r="Q13" s="137"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="129"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="136"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="138"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="127"/>
+      <c r="Q14" s="127"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="139"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="139"/>
-      <c r="L15" s="139"/>
-      <c r="M15" s="139"/>
-      <c r="N15" s="139"/>
-      <c r="O15" s="139"/>
-      <c r="P15" s="139"/>
-      <c r="Q15" s="139"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="139"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="125"/>
+      <c r="T15" s="125"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="120"/>
+      <c r="C16" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135" t="s">
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="142" t="s">
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="142"/>
-      <c r="Q16" s="142"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="144" t="s">
+      <c r="P16" s="122"/>
+      <c r="Q16" s="122"/>
+      <c r="R16" s="123"/>
+      <c r="S16" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="144"/>
+      <c r="T16" s="124"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="136"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="143" t="s">
+      <c r="A17" s="121"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="144"/>
-      <c r="Q17" s="144" t="s">
+      <c r="P17" s="124"/>
+      <c r="Q17" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="144"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
+      <c r="T17" s="124"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="148"/>
-      <c r="M18" s="148"/>
-      <c r="N18" s="148"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="149"/>
-      <c r="R18" s="149"/>
-      <c r="S18" s="149"/>
-      <c r="T18" s="149"/>
+      <c r="A18" s="115"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="119"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="145"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="145"/>
-      <c r="K19" s="145"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="145"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="145"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="145"/>
-      <c r="S19" s="145"/>
-      <c r="T19" s="145"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="110"/>
+      <c r="T19" s="110"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="145"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="145"/>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="145"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="145"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="145"/>
-      <c r="S20" s="145"/>
-      <c r="T20" s="145"/>
+      <c r="A20" s="110"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="110"/>
+      <c r="T20" s="110"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="151"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="151"/>
-      <c r="I21" s="151"/>
-      <c r="J21" s="151"/>
-      <c r="K21" s="151"/>
-      <c r="L21" s="151"/>
-      <c r="M21" s="151"/>
-      <c r="N21" s="151"/>
-      <c r="O21" s="153"/>
-      <c r="P21" s="151"/>
-      <c r="Q21" s="151"/>
-      <c r="R21" s="151"/>
-      <c r="S21" s="151"/>
-      <c r="T21" s="151"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -21551,6 +21115,59 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="B11:O11">
@@ -21933,51 +21550,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="111" t="str">
+      <c r="A2" s="136" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="112" t="s">
+      <c r="Q2" s="137" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114" t="s">
+      <c r="B3" s="139"/>
+      <c r="C3" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="113" t="s">
+      <c r="D3" s="139"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114" t="s">
+      <c r="G3" s="139"/>
+      <c r="H3" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="114"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="113" t="s">
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114" t="s">
+      <c r="L3" s="139"/>
+      <c r="M3" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="115"/>
+      <c r="N3" s="140"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -21989,10 +21606,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="116" t="s">
+      <c r="S3" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="117"/>
+      <c r="T3" s="142"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -22014,10 +21631,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="118" t="s">
+      <c r="R4" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="119"/>
+      <c r="S4" s="144"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -22043,8 +21660,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="121"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="146"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -22067,10 +21684,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="122" t="s">
+      <c r="R6" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="123"/>
+      <c r="S6" s="148"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -22093,10 +21710,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="124" t="s">
+      <c r="R7" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="125"/>
+      <c r="S7" s="150"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -22120,11 +21737,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="126" t="s">
+      <c r="R8" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="127"/>
-      <c r="T8" s="128"/>
+      <c r="S8" s="152"/>
+      <c r="T8" s="153"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -22146,10 +21763,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="109" t="s">
+      <c r="R9" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="110"/>
+      <c r="S9" s="135"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -22172,10 +21789,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="129" t="s">
+      <c r="R10" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="130"/>
+      <c r="S10" s="131"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -22201,8 +21818,8 @@
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="131"/>
-      <c r="T11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="118"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -22228,281 +21845,228 @@
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="134"/>
+      <c r="T12" s="112"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="135" t="s">
+      <c r="A13" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="137"/>
-      <c r="Q13" s="137"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="129"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="136"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="138"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="127"/>
+      <c r="Q14" s="127"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="139"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="139"/>
-      <c r="L15" s="139"/>
-      <c r="M15" s="139"/>
-      <c r="N15" s="139"/>
-      <c r="O15" s="139"/>
-      <c r="P15" s="139"/>
-      <c r="Q15" s="139"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="139"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="125"/>
+      <c r="T15" s="125"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="120"/>
+      <c r="C16" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135" t="s">
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="142" t="s">
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="142"/>
-      <c r="Q16" s="142"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="144" t="s">
+      <c r="P16" s="122"/>
+      <c r="Q16" s="122"/>
+      <c r="R16" s="123"/>
+      <c r="S16" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="144"/>
+      <c r="T16" s="124"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="136"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="143" t="s">
+      <c r="A17" s="121"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="144"/>
-      <c r="Q17" s="144" t="s">
+      <c r="P17" s="124"/>
+      <c r="Q17" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="144"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
+      <c r="T17" s="124"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="148"/>
-      <c r="M18" s="148"/>
-      <c r="N18" s="148"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="149"/>
-      <c r="R18" s="149"/>
-      <c r="S18" s="149"/>
-      <c r="T18" s="149"/>
+      <c r="A18" s="115"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="119"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="145"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="145"/>
-      <c r="K19" s="145"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="145"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="145"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="145"/>
-      <c r="S19" s="145"/>
-      <c r="T19" s="145"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="110"/>
+      <c r="T19" s="110"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="145"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="145"/>
-      <c r="K20" s="145"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="145"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="145"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="145"/>
-      <c r="S20" s="145"/>
-      <c r="T20" s="145"/>
+      <c r="A20" s="110"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="110"/>
+      <c r="T20" s="110"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="151"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="151"/>
-      <c r="I21" s="151"/>
-      <c r="J21" s="151"/>
-      <c r="K21" s="151"/>
-      <c r="L21" s="151"/>
-      <c r="M21" s="151"/>
-      <c r="N21" s="151"/>
-      <c r="O21" s="153"/>
-      <c r="P21" s="151"/>
-      <c r="Q21" s="151"/>
-      <c r="R21" s="151"/>
-      <c r="S21" s="151"/>
-      <c r="T21" s="151"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -22518,6 +22082,59 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="B11:O11">

--- a/public/frame.xlsx
+++ b/public/frame.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD51B83B-68E5-4028-B92F-137E05561B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF97D6D-504A-4208-9454-532C3B0F7274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="661" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1350,18 +1350,6 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1369,6 +1357,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1431,79 +1422,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="12" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1565,6 +1490,81 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6286,42 +6286,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48">
-      <c r="A1" s="82" t="str">
+      <c r="A1" s="106" t="str">
         <f>""&amp;default!A1&amp;"월 사회복무요원 근무계획"</f>
         <v>월 사회복무요원 근무계획</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="82"/>
-      <c r="T1" s="82"/>
-      <c r="U1" s="82"/>
-      <c r="V1" s="82"/>
-      <c r="W1" s="82"/>
-      <c r="X1" s="82"/>
-      <c r="Y1" s="82"/>
-      <c r="Z1" s="82"/>
-      <c r="AA1" s="82"/>
-      <c r="AB1" s="82"/>
-      <c r="AC1" s="82"/>
-      <c r="AD1" s="82"/>
-      <c r="AE1" s="82"/>
-      <c r="AF1" s="82"/>
-      <c r="AG1" s="82"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
+      <c r="AC1" s="106"/>
+      <c r="AD1" s="106"/>
+      <c r="AE1" s="106"/>
+      <c r="AF1" s="106"/>
+      <c r="AG1" s="106"/>
       <c r="AH1" s="1"/>
       <c r="AI1" s="2"/>
       <c r="AJ1" s="1"/>
@@ -6330,39 +6330,39 @@
       <c r="AM1" s="1"/>
     </row>
     <row r="2" spans="1:48">
-      <c r="A2" s="82"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="82"/>
-      <c r="N2" s="82"/>
-      <c r="O2" s="82"/>
-      <c r="P2" s="82"/>
-      <c r="Q2" s="82"/>
-      <c r="R2" s="82"/>
-      <c r="S2" s="82"/>
-      <c r="T2" s="82"/>
-      <c r="U2" s="82"/>
-      <c r="V2" s="82"/>
-      <c r="W2" s="82"/>
-      <c r="X2" s="82"/>
-      <c r="Y2" s="82"/>
-      <c r="Z2" s="82"/>
-      <c r="AA2" s="82"/>
-      <c r="AB2" s="82"/>
-      <c r="AC2" s="82"/>
-      <c r="AD2" s="82"/>
-      <c r="AE2" s="82"/>
-      <c r="AF2" s="82"/>
-      <c r="AG2" s="82"/>
+      <c r="A2" s="106"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="106"/>
+      <c r="R2" s="106"/>
+      <c r="S2" s="106"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="106"/>
+      <c r="V2" s="106"/>
+      <c r="W2" s="106"/>
+      <c r="X2" s="106"/>
+      <c r="Y2" s="106"/>
+      <c r="Z2" s="106"/>
+      <c r="AA2" s="106"/>
+      <c r="AB2" s="106"/>
+      <c r="AC2" s="106"/>
+      <c r="AD2" s="106"/>
+      <c r="AE2" s="106"/>
+      <c r="AF2" s="106"/>
+      <c r="AG2" s="106"/>
       <c r="AH2" s="1"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="1"/>
@@ -6371,39 +6371,39 @@
       <c r="AM2" s="1"/>
     </row>
     <row r="3" spans="1:48" ht="8.1" customHeight="1">
-      <c r="A3" s="83"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="W3" s="83"/>
-      <c r="X3" s="83"/>
-      <c r="Y3" s="83"/>
-      <c r="Z3" s="83"/>
-      <c r="AA3" s="83"/>
-      <c r="AB3" s="83"/>
-      <c r="AC3" s="83"/>
-      <c r="AD3" s="83"/>
-      <c r="AE3" s="83"/>
-      <c r="AF3" s="83"/>
-      <c r="AG3" s="83"/>
+      <c r="A3" s="107"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
+      <c r="O3" s="107"/>
+      <c r="P3" s="107"/>
+      <c r="Q3" s="107"/>
+      <c r="R3" s="107"/>
+      <c r="S3" s="107"/>
+      <c r="T3" s="107"/>
+      <c r="U3" s="107"/>
+      <c r="V3" s="107"/>
+      <c r="W3" s="107"/>
+      <c r="X3" s="107"/>
+      <c r="Y3" s="107"/>
+      <c r="Z3" s="107"/>
+      <c r="AA3" s="107"/>
+      <c r="AB3" s="107"/>
+      <c r="AC3" s="107"/>
+      <c r="AD3" s="107"/>
+      <c r="AE3" s="107"/>
+      <c r="AF3" s="107"/>
+      <c r="AG3" s="107"/>
       <c r="AH3" s="3"/>
       <c r="AI3" s="4"/>
       <c r="AJ3" s="5"/>
@@ -6412,10 +6412,10 @@
       <c r="AM3" s="5"/>
     </row>
     <row r="4" spans="1:48">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="84" t="s">
+      <c r="B4" s="108" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="7"/>
@@ -6459,13 +6459,13 @@
         <v>3</v>
       </c>
       <c r="AM4" s="5"/>
-      <c r="AN4" s="89" t="s">
+      <c r="AN4" s="86" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:48">
-      <c r="A5" s="84"/>
-      <c r="B5" s="84"/>
+      <c r="A5" s="108"/>
+      <c r="B5" s="108"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -6503,7 +6503,7 @@
       <c r="AK5" s="85"/>
       <c r="AL5" s="85"/>
       <c r="AM5" s="5"/>
-      <c r="AN5" s="90"/>
+      <c r="AN5" s="87"/>
     </row>
     <row r="6" spans="1:48">
       <c r="A6" s="6"/>
@@ -7987,28 +7987,28 @@
     </row>
     <row r="29" spans="1:48">
       <c r="A29" s="36"/>
-      <c r="B29" s="91" t="s">
+      <c r="B29" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="92"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="92"/>
-      <c r="F29" s="92"/>
-      <c r="G29" s="92"/>
-      <c r="H29" s="92"/>
-      <c r="I29" s="92"/>
-      <c r="J29" s="92"/>
-      <c r="K29" s="92"/>
-      <c r="L29" s="92"/>
-      <c r="M29" s="93"/>
-      <c r="N29" s="94"/>
-      <c r="O29" s="95"/>
-      <c r="P29" s="95"/>
-      <c r="Q29" s="95"/>
-      <c r="R29" s="95"/>
-      <c r="S29" s="95"/>
-      <c r="T29" s="95"/>
-      <c r="U29" s="96"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="89"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="89"/>
+      <c r="K29" s="89"/>
+      <c r="L29" s="89"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="91"/>
+      <c r="O29" s="92"/>
+      <c r="P29" s="92"/>
+      <c r="Q29" s="92"/>
+      <c r="R29" s="92"/>
+      <c r="S29" s="92"/>
+      <c r="T29" s="92"/>
+      <c r="U29" s="93"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
@@ -8041,28 +8041,28 @@
     </row>
     <row r="30" spans="1:48">
       <c r="A30" s="1"/>
-      <c r="B30" s="97" t="s">
+      <c r="B30" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="98"/>
-      <c r="D30" s="98"/>
-      <c r="E30" s="98"/>
-      <c r="F30" s="98"/>
-      <c r="G30" s="98"/>
-      <c r="H30" s="98"/>
-      <c r="I30" s="98"/>
-      <c r="J30" s="98"/>
-      <c r="K30" s="98"/>
-      <c r="L30" s="98"/>
-      <c r="M30" s="99"/>
-      <c r="N30" s="100"/>
-      <c r="O30" s="101"/>
-      <c r="P30" s="101"/>
-      <c r="Q30" s="101"/>
-      <c r="R30" s="101"/>
-      <c r="S30" s="101"/>
-      <c r="T30" s="101"/>
-      <c r="U30" s="102"/>
+      <c r="C30" s="95"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="95"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="95"/>
+      <c r="M30" s="96"/>
+      <c r="N30" s="97"/>
+      <c r="O30" s="98"/>
+      <c r="P30" s="98"/>
+      <c r="Q30" s="98"/>
+      <c r="R30" s="98"/>
+      <c r="S30" s="98"/>
+      <c r="T30" s="98"/>
+      <c r="U30" s="99"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
@@ -8094,28 +8094,28 @@
     </row>
     <row r="31" spans="1:48">
       <c r="A31" s="1"/>
-      <c r="B31" s="97" t="s">
+      <c r="B31" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="98"/>
-      <c r="D31" s="98"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="98"/>
-      <c r="G31" s="98"/>
-      <c r="H31" s="98"/>
-      <c r="I31" s="98"/>
-      <c r="J31" s="98"/>
-      <c r="K31" s="98"/>
-      <c r="L31" s="98"/>
-      <c r="M31" s="99"/>
-      <c r="N31" s="100"/>
-      <c r="O31" s="101"/>
-      <c r="P31" s="101"/>
-      <c r="Q31" s="101"/>
-      <c r="R31" s="101"/>
-      <c r="S31" s="101"/>
-      <c r="T31" s="101"/>
-      <c r="U31" s="102"/>
+      <c r="C31" s="95"/>
+      <c r="D31" s="95"/>
+      <c r="E31" s="95"/>
+      <c r="F31" s="95"/>
+      <c r="G31" s="95"/>
+      <c r="H31" s="95"/>
+      <c r="I31" s="95"/>
+      <c r="J31" s="95"/>
+      <c r="K31" s="95"/>
+      <c r="L31" s="95"/>
+      <c r="M31" s="96"/>
+      <c r="N31" s="97"/>
+      <c r="O31" s="98"/>
+      <c r="P31" s="98"/>
+      <c r="Q31" s="98"/>
+      <c r="R31" s="98"/>
+      <c r="S31" s="98"/>
+      <c r="T31" s="98"/>
+      <c r="U31" s="99"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
@@ -8151,28 +8151,28 @@
     </row>
     <row r="32" spans="1:48">
       <c r="A32" s="1"/>
-      <c r="B32" s="106" t="s">
+      <c r="B32" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="107"/>
-      <c r="D32" s="107"/>
-      <c r="E32" s="107"/>
-      <c r="F32" s="107"/>
-      <c r="G32" s="107"/>
-      <c r="H32" s="107"/>
-      <c r="I32" s="107"/>
-      <c r="J32" s="107"/>
-      <c r="K32" s="107"/>
-      <c r="L32" s="107"/>
-      <c r="M32" s="108"/>
-      <c r="N32" s="103"/>
-      <c r="O32" s="104"/>
-      <c r="P32" s="104"/>
-      <c r="Q32" s="104"/>
-      <c r="R32" s="104"/>
-      <c r="S32" s="104"/>
-      <c r="T32" s="104"/>
-      <c r="U32" s="105"/>
+      <c r="C32" s="104"/>
+      <c r="D32" s="104"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="104"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="104"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="104"/>
+      <c r="K32" s="104"/>
+      <c r="L32" s="104"/>
+      <c r="M32" s="105"/>
+      <c r="N32" s="100"/>
+      <c r="O32" s="101"/>
+      <c r="P32" s="101"/>
+      <c r="Q32" s="101"/>
+      <c r="R32" s="101"/>
+      <c r="S32" s="101"/>
+      <c r="T32" s="101"/>
+      <c r="U32" s="102"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
@@ -8205,18 +8205,18 @@
     </row>
     <row r="33" spans="1:40" ht="17.100000000000001" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="86"/>
-      <c r="G33" s="86"/>
-      <c r="H33" s="86"/>
-      <c r="I33" s="86"/>
-      <c r="J33" s="86"/>
-      <c r="K33" s="86"/>
-      <c r="L33" s="86"/>
-      <c r="M33" s="86"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="82"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
+      <c r="I33" s="82"/>
+      <c r="J33" s="82"/>
+      <c r="K33" s="82"/>
+      <c r="L33" s="82"/>
+      <c r="M33" s="82"/>
       <c r="N33" s="45"/>
       <c r="O33" s="45"/>
       <c r="P33" s="45"/>
@@ -8249,18 +8249,18 @@
     </row>
     <row r="34" spans="1:40">
       <c r="A34" s="1"/>
-      <c r="B34" s="87"/>
-      <c r="C34" s="87"/>
-      <c r="D34" s="87"/>
-      <c r="E34" s="87"/>
-      <c r="F34" s="87"/>
-      <c r="G34" s="87"/>
-      <c r="H34" s="87"/>
-      <c r="I34" s="87"/>
-      <c r="J34" s="87"/>
-      <c r="K34" s="87"/>
-      <c r="L34" s="87"/>
-      <c r="M34" s="87"/>
+      <c r="B34" s="83"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="83"/>
+      <c r="I34" s="83"/>
+      <c r="J34" s="83"/>
+      <c r="K34" s="83"/>
+      <c r="L34" s="83"/>
+      <c r="M34" s="83"/>
       <c r="N34" s="46"/>
       <c r="O34" s="46"/>
       <c r="P34" s="46"/>
@@ -8296,18 +8296,18 @@
     </row>
     <row r="35" spans="1:40">
       <c r="A35" s="1"/>
-      <c r="B35" s="88"/>
-      <c r="C35" s="88"/>
-      <c r="D35" s="88"/>
-      <c r="E35" s="88"/>
-      <c r="F35" s="88"/>
-      <c r="G35" s="88"/>
-      <c r="H35" s="88"/>
-      <c r="I35" s="88"/>
-      <c r="J35" s="88"/>
-      <c r="K35" s="88"/>
-      <c r="L35" s="88"/>
-      <c r="M35" s="88"/>
+      <c r="B35" s="84"/>
+      <c r="C35" s="84"/>
+      <c r="D35" s="84"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="84"/>
+      <c r="H35" s="84"/>
+      <c r="I35" s="84"/>
+      <c r="J35" s="84"/>
+      <c r="K35" s="84"/>
+      <c r="L35" s="84"/>
+      <c r="M35" s="84"/>
       <c r="N35" s="46"/>
       <c r="O35" s="46"/>
       <c r="P35" s="46"/>
@@ -8425,6 +8425,11 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:AG2"/>
+    <mergeCell ref="A3:AG3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="AK4:AK5"/>
     <mergeCell ref="B33:M33"/>
     <mergeCell ref="B34:M34"/>
     <mergeCell ref="B35:M35"/>
@@ -8436,11 +8441,6 @@
     <mergeCell ref="N30:U32"/>
     <mergeCell ref="B31:M31"/>
     <mergeCell ref="B32:M32"/>
-    <mergeCell ref="A1:AG2"/>
-    <mergeCell ref="A3:AG3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="AK4:AK5"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="B6">
@@ -10782,51 +10782,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="136" t="str">
+      <c r="A2" s="111" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="137" t="s">
+      <c r="Q2" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="138" t="s">
+      <c r="A3" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139" t="s">
+      <c r="B3" s="114"/>
+      <c r="C3" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="139"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="138" t="s">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139" t="s">
+      <c r="G3" s="114"/>
+      <c r="H3" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="138" t="s">
+      <c r="I3" s="114"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139" t="s">
+      <c r="L3" s="114"/>
+      <c r="M3" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="140"/>
+      <c r="N3" s="115"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -10838,10 +10838,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="141" t="s">
+      <c r="S3" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="142"/>
+      <c r="T3" s="117"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -10863,10 +10863,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="143" t="s">
+      <c r="R4" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="144"/>
+      <c r="S4" s="119"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -10892,8 +10892,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="146"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="121"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -10916,10 +10916,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="147" t="s">
+      <c r="R6" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="148"/>
+      <c r="S6" s="123"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -10942,10 +10942,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="149" t="s">
+      <c r="R7" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="150"/>
+      <c r="S7" s="125"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -10969,11 +10969,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="151" t="s">
+      <c r="R8" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="152"/>
-      <c r="T8" s="153"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="128"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -10995,10 +10995,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="134" t="s">
+      <c r="R9" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="135"/>
+      <c r="S9" s="110"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -11021,10 +11021,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="130" t="s">
+      <c r="R10" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="131"/>
+      <c r="S10" s="130"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -11045,13 +11045,13 @@
       <c r="M11" s="63"/>
       <c r="N11" s="63"/>
       <c r="O11" s="63"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="132"/>
-      <c r="T11" s="118"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="132"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -11071,234 +11071,287 @@
       <c r="M12" s="61"/>
       <c r="N12" s="61"/>
       <c r="O12" s="61"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="61"/>
       <c r="R12" s="59" t="s">
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="112"/>
+      <c r="T12" s="134"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="120" t="s">
+      <c r="A13" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
-      <c r="P13" s="126"/>
-      <c r="Q13" s="126"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="135"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="128"/>
-      <c r="T13" s="129"/>
+      <c r="S13" s="140"/>
+      <c r="T13" s="141"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="127"/>
-      <c r="Q14" s="127"/>
+      <c r="A14" s="136"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="125"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="125"/>
-      <c r="T15" s="125"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120" t="s">
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="122" t="s">
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="122"/>
-      <c r="Q16" s="122"/>
-      <c r="R16" s="123"/>
-      <c r="S16" s="124" t="s">
+      <c r="P16" s="142"/>
+      <c r="Q16" s="142"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="124"/>
+      <c r="T16" s="144"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="121"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="123" t="s">
+      <c r="A17" s="136"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124" t="s">
+      <c r="P17" s="144"/>
+      <c r="Q17" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="144"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="119"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="148"/>
+      <c r="L18" s="148"/>
+      <c r="M18" s="148"/>
+      <c r="N18" s="148"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="149"/>
+      <c r="Q18" s="149"/>
+      <c r="R18" s="149"/>
+      <c r="S18" s="149"/>
+      <c r="T18" s="149"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="110"/>
+      <c r="A19" s="145"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="110"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110"/>
+      <c r="A20" s="145"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="145"/>
+      <c r="T20" s="145"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
+      <c r="A21" s="151"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="151"/>
+      <c r="I21" s="151"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="151"/>
+      <c r="M21" s="151"/>
+      <c r="N21" s="151"/>
+      <c r="O21" s="153"/>
+      <c r="P21" s="151"/>
+      <c r="Q21" s="151"/>
+      <c r="R21" s="151"/>
+      <c r="S21" s="151"/>
+      <c r="T21" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -11314,62 +11367,9 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="B11:O11">
+  <conditionalFormatting sqref="B11:Q11">
     <cfRule type="cellIs" dxfId="59" priority="3" operator="equal">
       <formula>"연"</formula>
     </cfRule>
@@ -11749,51 +11749,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="136" t="str">
+      <c r="A2" s="111" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="137" t="s">
+      <c r="Q2" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="138" t="s">
+      <c r="A3" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139" t="s">
+      <c r="B3" s="114"/>
+      <c r="C3" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="139"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="138" t="s">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139" t="s">
+      <c r="G3" s="114"/>
+      <c r="H3" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="138" t="s">
+      <c r="I3" s="114"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139" t="s">
+      <c r="L3" s="114"/>
+      <c r="M3" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="140"/>
+      <c r="N3" s="115"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -11805,10 +11805,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="141" t="s">
+      <c r="S3" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="142"/>
+      <c r="T3" s="117"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -11830,10 +11830,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="143" t="s">
+      <c r="R4" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="144"/>
+      <c r="S4" s="119"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -11859,8 +11859,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="146"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="121"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -11883,10 +11883,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="147" t="s">
+      <c r="R6" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="148"/>
+      <c r="S6" s="123"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -11909,10 +11909,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="149" t="s">
+      <c r="R7" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="150"/>
+      <c r="S7" s="125"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -11936,11 +11936,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="151" t="s">
+      <c r="R8" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="152"/>
-      <c r="T8" s="153"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="128"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -11962,10 +11962,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="134" t="s">
+      <c r="R9" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="135"/>
+      <c r="S9" s="110"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -11988,10 +11988,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="130" t="s">
+      <c r="R10" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="131"/>
+      <c r="S10" s="130"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -12012,13 +12012,13 @@
       <c r="M11" s="63"/>
       <c r="N11" s="63"/>
       <c r="O11" s="63"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="132"/>
-      <c r="T11" s="118"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="132"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -12038,234 +12038,287 @@
       <c r="M12" s="61"/>
       <c r="N12" s="61"/>
       <c r="O12" s="61"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="61"/>
       <c r="R12" s="59" t="s">
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="112"/>
+      <c r="T12" s="134"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="120" t="s">
+      <c r="A13" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
-      <c r="P13" s="126"/>
-      <c r="Q13" s="126"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="135"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="128"/>
-      <c r="T13" s="129"/>
+      <c r="S13" s="140"/>
+      <c r="T13" s="141"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="127"/>
-      <c r="Q14" s="127"/>
+      <c r="A14" s="136"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="125"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="125"/>
-      <c r="T15" s="125"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120" t="s">
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="122" t="s">
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="122"/>
-      <c r="Q16" s="122"/>
-      <c r="R16" s="123"/>
-      <c r="S16" s="124" t="s">
+      <c r="P16" s="142"/>
+      <c r="Q16" s="142"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="124"/>
+      <c r="T16" s="144"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="121"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="123" t="s">
+      <c r="A17" s="136"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124" t="s">
+      <c r="P17" s="144"/>
+      <c r="Q17" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="144"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="119"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="148"/>
+      <c r="L18" s="148"/>
+      <c r="M18" s="148"/>
+      <c r="N18" s="148"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="149"/>
+      <c r="Q18" s="149"/>
+      <c r="R18" s="149"/>
+      <c r="S18" s="149"/>
+      <c r="T18" s="149"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="110"/>
+      <c r="A19" s="145"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="110"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110"/>
+      <c r="A20" s="145"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="145"/>
+      <c r="T20" s="145"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
+      <c r="A21" s="151"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="151"/>
+      <c r="I21" s="151"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="151"/>
+      <c r="M21" s="151"/>
+      <c r="N21" s="151"/>
+      <c r="O21" s="153"/>
+      <c r="P21" s="151"/>
+      <c r="Q21" s="151"/>
+      <c r="R21" s="151"/>
+      <c r="S21" s="151"/>
+      <c r="T21" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -12281,62 +12334,9 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="B11:O11">
+  <conditionalFormatting sqref="B11:Q11">
     <cfRule type="cellIs" dxfId="49" priority="3" operator="equal">
       <formula>"연"</formula>
     </cfRule>
@@ -12716,51 +12716,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="136" t="str">
+      <c r="A2" s="111" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="137" t="s">
+      <c r="Q2" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="138" t="s">
+      <c r="A3" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139" t="s">
+      <c r="B3" s="114"/>
+      <c r="C3" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="139"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="138" t="s">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139" t="s">
+      <c r="G3" s="114"/>
+      <c r="H3" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="138" t="s">
+      <c r="I3" s="114"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139" t="s">
+      <c r="L3" s="114"/>
+      <c r="M3" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="140"/>
+      <c r="N3" s="115"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -12772,10 +12772,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="141" t="s">
+      <c r="S3" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="142"/>
+      <c r="T3" s="117"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -12797,8 +12797,8 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="143"/>
-      <c r="S4" s="144"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="119"/>
       <c r="T4" s="73"/>
       <c r="V4" s="72"/>
     </row>
@@ -12822,8 +12822,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="146"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="121"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -12846,8 +12846,8 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="147"/>
-      <c r="S6" s="148"/>
+      <c r="R6" s="122"/>
+      <c r="S6" s="123"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -12870,8 +12870,8 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="149"/>
-      <c r="S7" s="150"/>
+      <c r="R7" s="124"/>
+      <c r="S7" s="125"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -12895,9 +12895,9 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="151"/>
-      <c r="S8" s="152"/>
-      <c r="T8" s="153"/>
+      <c r="R8" s="126"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="128"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -12919,8 +12919,8 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="134"/>
-      <c r="S9" s="135"/>
+      <c r="R9" s="109"/>
+      <c r="S9" s="110"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -12943,8 +12943,8 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="130"/>
-      <c r="S10" s="131"/>
+      <c r="R10" s="129"/>
+      <c r="S10" s="130"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -12965,11 +12965,11 @@
       <c r="M11" s="63"/>
       <c r="N11" s="63"/>
       <c r="O11" s="63"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
       <c r="R11" s="62"/>
-      <c r="S11" s="132"/>
-      <c r="T11" s="118"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="132"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -12989,230 +12989,283 @@
       <c r="M12" s="61"/>
       <c r="N12" s="61"/>
       <c r="O12" s="61"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="61"/>
       <c r="R12" s="59"/>
       <c r="S12" s="133"/>
-      <c r="T12" s="112"/>
+      <c r="T12" s="134"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="120" t="s">
+      <c r="A13" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
-      <c r="P13" s="126"/>
-      <c r="Q13" s="126"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="135"/>
       <c r="R13" s="58"/>
-      <c r="S13" s="128"/>
-      <c r="T13" s="129"/>
+      <c r="S13" s="140"/>
+      <c r="T13" s="141"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="127"/>
-      <c r="Q14" s="127"/>
+      <c r="A14" s="136"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="125"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="125"/>
-      <c r="T15" s="125"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120" t="s">
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="122" t="s">
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="122"/>
-      <c r="Q16" s="122"/>
-      <c r="R16" s="123"/>
-      <c r="S16" s="124" t="s">
+      <c r="P16" s="142"/>
+      <c r="Q16" s="142"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="124"/>
+      <c r="T16" s="144"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="121"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="123" t="s">
+      <c r="A17" s="136"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124" t="s">
+      <c r="P17" s="144"/>
+      <c r="Q17" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="144"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="119"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="148"/>
+      <c r="L18" s="148"/>
+      <c r="M18" s="148"/>
+      <c r="N18" s="148"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="149"/>
+      <c r="Q18" s="149"/>
+      <c r="R18" s="149"/>
+      <c r="S18" s="149"/>
+      <c r="T18" s="149"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="110"/>
+      <c r="A19" s="145"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="110"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110"/>
+      <c r="A20" s="145"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="145"/>
+      <c r="T20" s="145"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
+      <c r="A21" s="151"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="151"/>
+      <c r="I21" s="151"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="151"/>
+      <c r="M21" s="151"/>
+      <c r="N21" s="151"/>
+      <c r="O21" s="153"/>
+      <c r="P21" s="151"/>
+      <c r="Q21" s="151"/>
+      <c r="R21" s="151"/>
+      <c r="S21" s="151"/>
+      <c r="T21" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -13228,62 +13281,9 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="B11:O11">
+  <conditionalFormatting sqref="B11:Q11">
     <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
       <formula>"연"</formula>
     </cfRule>
@@ -13663,51 +13663,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="136" t="str">
+      <c r="A2" s="111" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="137" t="s">
+      <c r="Q2" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="138" t="s">
+      <c r="A3" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139" t="s">
+      <c r="B3" s="114"/>
+      <c r="C3" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="139"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="138" t="s">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139" t="s">
+      <c r="G3" s="114"/>
+      <c r="H3" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="138" t="s">
+      <c r="I3" s="114"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139" t="s">
+      <c r="L3" s="114"/>
+      <c r="M3" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="140"/>
+      <c r="N3" s="115"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -13719,10 +13719,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="141" t="s">
+      <c r="S3" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="142"/>
+      <c r="T3" s="117"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -13744,10 +13744,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="143" t="s">
+      <c r="R4" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="144"/>
+      <c r="S4" s="119"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -13773,8 +13773,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="146"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="121"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -13797,10 +13797,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="147" t="s">
+      <c r="R6" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="148"/>
+      <c r="S6" s="123"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -13823,10 +13823,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="149" t="s">
+      <c r="R7" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="150"/>
+      <c r="S7" s="125"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -13850,11 +13850,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="151" t="s">
+      <c r="R8" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="152"/>
-      <c r="T8" s="153"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="128"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -13876,10 +13876,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="134" t="s">
+      <c r="R9" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="135"/>
+      <c r="S9" s="110"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -13902,10 +13902,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="130" t="s">
+      <c r="R10" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="131"/>
+      <c r="S10" s="130"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -13926,13 +13926,13 @@
       <c r="M11" s="63"/>
       <c r="N11" s="63"/>
       <c r="O11" s="63"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="132"/>
-      <c r="T11" s="118"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="132"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -13952,234 +13952,287 @@
       <c r="M12" s="61"/>
       <c r="N12" s="61"/>
       <c r="O12" s="61"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="61"/>
       <c r="R12" s="59" t="s">
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="112"/>
+      <c r="T12" s="134"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="120" t="s">
+      <c r="A13" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
-      <c r="P13" s="126"/>
-      <c r="Q13" s="126"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="135"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="128"/>
-      <c r="T13" s="129"/>
+      <c r="S13" s="140"/>
+      <c r="T13" s="141"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="127"/>
-      <c r="Q14" s="127"/>
+      <c r="A14" s="136"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="125"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="125"/>
-      <c r="T15" s="125"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120" t="s">
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="122" t="s">
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="122"/>
-      <c r="Q16" s="122"/>
-      <c r="R16" s="123"/>
-      <c r="S16" s="124" t="s">
+      <c r="P16" s="142"/>
+      <c r="Q16" s="142"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="124"/>
+      <c r="T16" s="144"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="121"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="123" t="s">
+      <c r="A17" s="136"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124" t="s">
+      <c r="P17" s="144"/>
+      <c r="Q17" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="144"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="119"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="148"/>
+      <c r="L18" s="148"/>
+      <c r="M18" s="148"/>
+      <c r="N18" s="148"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="149"/>
+      <c r="Q18" s="149"/>
+      <c r="R18" s="149"/>
+      <c r="S18" s="149"/>
+      <c r="T18" s="149"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="110"/>
+      <c r="A19" s="145"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="110"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110"/>
+      <c r="A20" s="145"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="145"/>
+      <c r="T20" s="145"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
+      <c r="A21" s="151"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="151"/>
+      <c r="I21" s="151"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="151"/>
+      <c r="M21" s="151"/>
+      <c r="N21" s="151"/>
+      <c r="O21" s="153"/>
+      <c r="P21" s="151"/>
+      <c r="Q21" s="151"/>
+      <c r="R21" s="151"/>
+      <c r="S21" s="151"/>
+      <c r="T21" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -14195,62 +14248,9 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="B11:O11">
+  <conditionalFormatting sqref="B11:Q11">
     <cfRule type="cellIs" dxfId="29" priority="3" operator="equal">
       <formula>"연"</formula>
     </cfRule>
@@ -14630,51 +14630,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="136" t="str">
+      <c r="A2" s="111" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="137" t="s">
+      <c r="Q2" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="138" t="s">
+      <c r="A3" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139" t="s">
+      <c r="B3" s="114"/>
+      <c r="C3" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="139"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="138" t="s">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139" t="s">
+      <c r="G3" s="114"/>
+      <c r="H3" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="138" t="s">
+      <c r="I3" s="114"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139" t="s">
+      <c r="L3" s="114"/>
+      <c r="M3" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="140"/>
+      <c r="N3" s="115"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -14686,10 +14686,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="141" t="s">
+      <c r="S3" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="142"/>
+      <c r="T3" s="117"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -14711,10 +14711,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="143" t="s">
+      <c r="R4" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="144"/>
+      <c r="S4" s="119"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -14740,8 +14740,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="146"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="121"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -14764,10 +14764,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="147" t="s">
+      <c r="R6" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="148"/>
+      <c r="S6" s="123"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -14790,10 +14790,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="149" t="s">
+      <c r="R7" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="150"/>
+      <c r="S7" s="125"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -14817,11 +14817,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="151" t="s">
+      <c r="R8" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="152"/>
-      <c r="T8" s="153"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="128"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -14843,10 +14843,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="134" t="s">
+      <c r="R9" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="135"/>
+      <c r="S9" s="110"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -14869,10 +14869,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="130" t="s">
+      <c r="R10" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="131"/>
+      <c r="S10" s="130"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -14893,13 +14893,13 @@
       <c r="M11" s="63"/>
       <c r="N11" s="63"/>
       <c r="O11" s="63"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="132"/>
-      <c r="T11" s="118"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="132"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -14919,234 +14919,287 @@
       <c r="M12" s="61"/>
       <c r="N12" s="61"/>
       <c r="O12" s="61"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="61"/>
       <c r="R12" s="59" t="s">
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="112"/>
+      <c r="T12" s="134"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="120" t="s">
+      <c r="A13" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
-      <c r="P13" s="126"/>
-      <c r="Q13" s="126"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="135"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="128"/>
-      <c r="T13" s="129"/>
+      <c r="S13" s="140"/>
+      <c r="T13" s="141"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="127"/>
-      <c r="Q14" s="127"/>
+      <c r="A14" s="136"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="125"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="125"/>
-      <c r="T15" s="125"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120" t="s">
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="122" t="s">
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="122"/>
-      <c r="Q16" s="122"/>
-      <c r="R16" s="123"/>
-      <c r="S16" s="124" t="s">
+      <c r="P16" s="142"/>
+      <c r="Q16" s="142"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="124"/>
+      <c r="T16" s="144"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="121"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="123" t="s">
+      <c r="A17" s="136"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124" t="s">
+      <c r="P17" s="144"/>
+      <c r="Q17" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="144"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="119"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="148"/>
+      <c r="L18" s="148"/>
+      <c r="M18" s="148"/>
+      <c r="N18" s="148"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="149"/>
+      <c r="Q18" s="149"/>
+      <c r="R18" s="149"/>
+      <c r="S18" s="149"/>
+      <c r="T18" s="149"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="110"/>
+      <c r="A19" s="145"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="110"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110"/>
+      <c r="A20" s="145"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="145"/>
+      <c r="T20" s="145"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
+      <c r="A21" s="151"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="151"/>
+      <c r="I21" s="151"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="151"/>
+      <c r="M21" s="151"/>
+      <c r="N21" s="151"/>
+      <c r="O21" s="153"/>
+      <c r="P21" s="151"/>
+      <c r="Q21" s="151"/>
+      <c r="R21" s="151"/>
+      <c r="S21" s="151"/>
+      <c r="T21" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -15162,62 +15215,9 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="B11:O11">
+  <conditionalFormatting sqref="B11:Q11">
     <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"연"</formula>
     </cfRule>
@@ -15597,51 +15597,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="136" t="str">
+      <c r="A2" s="111" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="137" t="s">
+      <c r="Q2" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="138" t="s">
+      <c r="A3" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139" t="s">
+      <c r="B3" s="114"/>
+      <c r="C3" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="139"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="138" t="s">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139" t="s">
+      <c r="G3" s="114"/>
+      <c r="H3" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="138" t="s">
+      <c r="I3" s="114"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139" t="s">
+      <c r="L3" s="114"/>
+      <c r="M3" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="140"/>
+      <c r="N3" s="115"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -15653,10 +15653,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="141" t="s">
+      <c r="S3" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="142"/>
+      <c r="T3" s="117"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -15678,10 +15678,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="143" t="s">
+      <c r="R4" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="144"/>
+      <c r="S4" s="119"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -15707,8 +15707,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="146"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="121"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -15731,10 +15731,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="147" t="s">
+      <c r="R6" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="148"/>
+      <c r="S6" s="123"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -15757,10 +15757,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="149" t="s">
+      <c r="R7" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="150"/>
+      <c r="S7" s="125"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -15784,11 +15784,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="151" t="s">
+      <c r="R8" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="152"/>
-      <c r="T8" s="153"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="128"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -15810,10 +15810,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="134" t="s">
+      <c r="R9" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="135"/>
+      <c r="S9" s="110"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -15836,10 +15836,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="130" t="s">
+      <c r="R10" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="131"/>
+      <c r="S10" s="130"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -15860,13 +15860,13 @@
       <c r="M11" s="63"/>
       <c r="N11" s="63"/>
       <c r="O11" s="63"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="132"/>
-      <c r="T11" s="118"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="132"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -15886,259 +15886,265 @@
       <c r="M12" s="61"/>
       <c r="N12" s="61"/>
       <c r="O12" s="61"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="61"/>
       <c r="R12" s="59" t="s">
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="112"/>
+      <c r="T12" s="134"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="120" t="s">
+      <c r="A13" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
-      <c r="P13" s="126"/>
-      <c r="Q13" s="126"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="135"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="128"/>
-      <c r="T13" s="129"/>
+      <c r="S13" s="140"/>
+      <c r="T13" s="141"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="127"/>
-      <c r="Q14" s="127"/>
+      <c r="A14" s="136"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="125"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="125"/>
-      <c r="T15" s="125"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120" t="s">
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="122" t="s">
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="122"/>
-      <c r="Q16" s="122"/>
-      <c r="R16" s="123"/>
-      <c r="S16" s="124" t="s">
+      <c r="P16" s="142"/>
+      <c r="Q16" s="142"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="124"/>
+      <c r="T16" s="144"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="121"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="123" t="s">
+      <c r="A17" s="136"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124" t="s">
+      <c r="P17" s="144"/>
+      <c r="Q17" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="144"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="119"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="148"/>
+      <c r="L18" s="148"/>
+      <c r="M18" s="148"/>
+      <c r="N18" s="148"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="149"/>
+      <c r="Q18" s="149"/>
+      <c r="R18" s="149"/>
+      <c r="S18" s="149"/>
+      <c r="T18" s="149"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="110"/>
+      <c r="A19" s="145"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="110"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110"/>
+      <c r="A20" s="145"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="145"/>
+      <c r="T20" s="145"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
+      <c r="A21" s="151"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="151"/>
+      <c r="I21" s="151"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="151"/>
+      <c r="M21" s="151"/>
+      <c r="N21" s="151"/>
+      <c r="O21" s="153"/>
+      <c r="P21" s="151"/>
+      <c r="Q21" s="151"/>
+      <c r="R21" s="151"/>
+      <c r="S21" s="151"/>
+      <c r="T21" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
     <mergeCell ref="A15:T15"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="I13:I14"/>
@@ -16151,40 +16157,34 @@
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="S3:T3"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="B11:O11">
+  <conditionalFormatting sqref="B11:Q11">
     <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"연"</formula>
     </cfRule>
@@ -16715,51 +16715,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="136" t="str">
+      <c r="A2" s="111" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="137" t="s">
+      <c r="Q2" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="138" t="s">
+      <c r="A3" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139" t="s">
+      <c r="B3" s="114"/>
+      <c r="C3" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="139"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="138" t="s">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139" t="s">
+      <c r="G3" s="114"/>
+      <c r="H3" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="138" t="s">
+      <c r="I3" s="114"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139" t="s">
+      <c r="L3" s="114"/>
+      <c r="M3" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="140"/>
+      <c r="N3" s="115"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -16771,10 +16771,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="141" t="s">
+      <c r="S3" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="142"/>
+      <c r="T3" s="117"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -16796,10 +16796,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="143" t="s">
+      <c r="R4" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="144"/>
+      <c r="S4" s="119"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -16825,8 +16825,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="146"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="121"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -16849,10 +16849,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="147" t="s">
+      <c r="R6" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="148"/>
+      <c r="S6" s="123"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -16875,10 +16875,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="149" t="s">
+      <c r="R7" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="150"/>
+      <c r="S7" s="125"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -16902,11 +16902,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="151" t="s">
+      <c r="R8" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="152"/>
-      <c r="T8" s="153"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="128"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -16928,10 +16928,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="134" t="s">
+      <c r="R9" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="135"/>
+      <c r="S9" s="110"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -16954,10 +16954,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="130" t="s">
+      <c r="R10" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="131"/>
+      <c r="S10" s="130"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -16978,13 +16978,13 @@
       <c r="M11" s="63"/>
       <c r="N11" s="63"/>
       <c r="O11" s="63"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="132"/>
-      <c r="T11" s="118"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="132"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -17004,234 +17004,287 @@
       <c r="M12" s="61"/>
       <c r="N12" s="61"/>
       <c r="O12" s="61"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="61"/>
       <c r="R12" s="59" t="s">
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="112"/>
+      <c r="T12" s="134"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="120" t="s">
+      <c r="A13" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
-      <c r="P13" s="126"/>
-      <c r="Q13" s="126"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="135"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="128"/>
-      <c r="T13" s="129"/>
+      <c r="S13" s="140"/>
+      <c r="T13" s="141"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="127"/>
-      <c r="Q14" s="127"/>
+      <c r="A14" s="136"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="125"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="125"/>
-      <c r="T15" s="125"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120" t="s">
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="122" t="s">
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="122"/>
-      <c r="Q16" s="122"/>
-      <c r="R16" s="123"/>
-      <c r="S16" s="124" t="s">
+      <c r="P16" s="142"/>
+      <c r="Q16" s="142"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="124"/>
+      <c r="T16" s="144"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="121"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="123" t="s">
+      <c r="A17" s="136"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124" t="s">
+      <c r="P17" s="144"/>
+      <c r="Q17" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="144"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="119"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="148"/>
+      <c r="L18" s="148"/>
+      <c r="M18" s="148"/>
+      <c r="N18" s="148"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="149"/>
+      <c r="Q18" s="149"/>
+      <c r="R18" s="149"/>
+      <c r="S18" s="149"/>
+      <c r="T18" s="149"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="110"/>
+      <c r="A19" s="145"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="110"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110"/>
+      <c r="A20" s="145"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="145"/>
+      <c r="T20" s="145"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
+      <c r="A21" s="151"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="151"/>
+      <c r="I21" s="151"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="151"/>
+      <c r="M21" s="151"/>
+      <c r="N21" s="151"/>
+      <c r="O21" s="153"/>
+      <c r="P21" s="151"/>
+      <c r="Q21" s="151"/>
+      <c r="R21" s="151"/>
+      <c r="S21" s="151"/>
+      <c r="T21" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -17247,62 +17300,9 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="B11:O11">
+  <conditionalFormatting sqref="B11:Q11">
     <cfRule type="cellIs" dxfId="119" priority="3" operator="equal">
       <formula>"연"</formula>
     </cfRule>
@@ -17682,51 +17682,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="136" t="str">
+      <c r="A2" s="111" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="137" t="s">
+      <c r="Q2" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="138" t="s">
+      <c r="A3" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139" t="s">
+      <c r="B3" s="114"/>
+      <c r="C3" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="139"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="138" t="s">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139" t="s">
+      <c r="G3" s="114"/>
+      <c r="H3" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="138" t="s">
+      <c r="I3" s="114"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139" t="s">
+      <c r="L3" s="114"/>
+      <c r="M3" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="140"/>
+      <c r="N3" s="115"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -17738,10 +17738,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="141" t="s">
+      <c r="S3" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="142"/>
+      <c r="T3" s="117"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -17763,10 +17763,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="143" t="s">
+      <c r="R4" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="144"/>
+      <c r="S4" s="119"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -17792,8 +17792,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="146"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="121"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -17816,10 +17816,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="147" t="s">
+      <c r="R6" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="148"/>
+      <c r="S6" s="123"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -17842,10 +17842,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="149" t="s">
+      <c r="R7" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="150"/>
+      <c r="S7" s="125"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -17869,11 +17869,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="151" t="s">
+      <c r="R8" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="152"/>
-      <c r="T8" s="153"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="128"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -17895,10 +17895,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="134" t="s">
+      <c r="R9" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="135"/>
+      <c r="S9" s="110"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -17921,10 +17921,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="130" t="s">
+      <c r="R10" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="131"/>
+      <c r="S10" s="130"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -17945,13 +17945,13 @@
       <c r="M11" s="63"/>
       <c r="N11" s="63"/>
       <c r="O11" s="63"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="132"/>
-      <c r="T11" s="118"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="132"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -17971,234 +17971,287 @@
       <c r="M12" s="61"/>
       <c r="N12" s="61"/>
       <c r="O12" s="61"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="61"/>
       <c r="R12" s="59" t="s">
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="112"/>
+      <c r="T12" s="134"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="120" t="s">
+      <c r="A13" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
-      <c r="P13" s="126"/>
-      <c r="Q13" s="126"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="135"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="128"/>
-      <c r="T13" s="129"/>
+      <c r="S13" s="140"/>
+      <c r="T13" s="141"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="127"/>
-      <c r="Q14" s="127"/>
+      <c r="A14" s="136"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="125"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="125"/>
-      <c r="T15" s="125"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120" t="s">
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="122" t="s">
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="122"/>
-      <c r="Q16" s="122"/>
-      <c r="R16" s="123"/>
-      <c r="S16" s="124" t="s">
+      <c r="P16" s="142"/>
+      <c r="Q16" s="142"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="124"/>
+      <c r="T16" s="144"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="121"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="123" t="s">
+      <c r="A17" s="136"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124" t="s">
+      <c r="P17" s="144"/>
+      <c r="Q17" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="144"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="119"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="148"/>
+      <c r="L18" s="148"/>
+      <c r="M18" s="148"/>
+      <c r="N18" s="148"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="149"/>
+      <c r="Q18" s="149"/>
+      <c r="R18" s="149"/>
+      <c r="S18" s="149"/>
+      <c r="T18" s="149"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="110"/>
+      <c r="A19" s="145"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="110"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110"/>
+      <c r="A20" s="145"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="145"/>
+      <c r="T20" s="145"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
+      <c r="A21" s="151"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="151"/>
+      <c r="I21" s="151"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="151"/>
+      <c r="M21" s="151"/>
+      <c r="N21" s="151"/>
+      <c r="O21" s="153"/>
+      <c r="P21" s="151"/>
+      <c r="Q21" s="151"/>
+      <c r="R21" s="151"/>
+      <c r="S21" s="151"/>
+      <c r="T21" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -18214,62 +18267,9 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="B11:O11">
+  <conditionalFormatting sqref="B11:Q11">
     <cfRule type="cellIs" dxfId="109" priority="3" operator="equal">
       <formula>"연"</formula>
     </cfRule>
@@ -18649,51 +18649,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="136" t="str">
+      <c r="A2" s="111" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="137" t="s">
+      <c r="Q2" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="138" t="s">
+      <c r="A3" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139" t="s">
+      <c r="B3" s="114"/>
+      <c r="C3" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="139"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="138" t="s">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139" t="s">
+      <c r="G3" s="114"/>
+      <c r="H3" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="138" t="s">
+      <c r="I3" s="114"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139" t="s">
+      <c r="L3" s="114"/>
+      <c r="M3" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="140"/>
+      <c r="N3" s="115"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -18705,10 +18705,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="141" t="s">
+      <c r="S3" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="142"/>
+      <c r="T3" s="117"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -18730,10 +18730,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="143" t="s">
+      <c r="R4" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="144"/>
+      <c r="S4" s="119"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -18759,8 +18759,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="146"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="121"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -18783,10 +18783,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="147" t="s">
+      <c r="R6" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="148"/>
+      <c r="S6" s="123"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -18809,10 +18809,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="149" t="s">
+      <c r="R7" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="150"/>
+      <c r="S7" s="125"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -18836,11 +18836,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="151" t="s">
+      <c r="R8" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="152"/>
-      <c r="T8" s="153"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="128"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -18862,10 +18862,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="134" t="s">
+      <c r="R9" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="135"/>
+      <c r="S9" s="110"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -18888,10 +18888,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="130" t="s">
+      <c r="R10" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="131"/>
+      <c r="S10" s="130"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -18912,13 +18912,13 @@
       <c r="M11" s="63"/>
       <c r="N11" s="63"/>
       <c r="O11" s="63"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="132"/>
-      <c r="T11" s="118"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="132"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -18938,234 +18938,287 @@
       <c r="M12" s="61"/>
       <c r="N12" s="61"/>
       <c r="O12" s="61"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="61"/>
       <c r="R12" s="59" t="s">
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="112"/>
+      <c r="T12" s="134"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="120" t="s">
+      <c r="A13" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
-      <c r="P13" s="126"/>
-      <c r="Q13" s="126"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="135"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="128"/>
-      <c r="T13" s="129"/>
+      <c r="S13" s="140"/>
+      <c r="T13" s="141"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="127"/>
-      <c r="Q14" s="127"/>
+      <c r="A14" s="136"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="125"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="125"/>
-      <c r="T15" s="125"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120" t="s">
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="122" t="s">
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="122"/>
-      <c r="Q16" s="122"/>
-      <c r="R16" s="123"/>
-      <c r="S16" s="124" t="s">
+      <c r="P16" s="142"/>
+      <c r="Q16" s="142"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="124"/>
+      <c r="T16" s="144"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="121"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="123" t="s">
+      <c r="A17" s="136"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124" t="s">
+      <c r="P17" s="144"/>
+      <c r="Q17" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="144"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="119"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="148"/>
+      <c r="L18" s="148"/>
+      <c r="M18" s="148"/>
+      <c r="N18" s="148"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="149"/>
+      <c r="Q18" s="149"/>
+      <c r="R18" s="149"/>
+      <c r="S18" s="149"/>
+      <c r="T18" s="149"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="110"/>
+      <c r="A19" s="145"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="110"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110"/>
+      <c r="A20" s="145"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="145"/>
+      <c r="T20" s="145"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
+      <c r="A21" s="151"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="151"/>
+      <c r="I21" s="151"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="151"/>
+      <c r="M21" s="151"/>
+      <c r="N21" s="151"/>
+      <c r="O21" s="153"/>
+      <c r="P21" s="151"/>
+      <c r="Q21" s="151"/>
+      <c r="R21" s="151"/>
+      <c r="S21" s="151"/>
+      <c r="T21" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -19181,62 +19234,9 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="B11:O11">
+  <conditionalFormatting sqref="B11:Q11">
     <cfRule type="cellIs" dxfId="99" priority="3" operator="equal">
       <formula>"연"</formula>
     </cfRule>
@@ -19616,51 +19616,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="136" t="str">
+      <c r="A2" s="111" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="137" t="s">
+      <c r="Q2" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="138" t="s">
+      <c r="A3" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139" t="s">
+      <c r="B3" s="114"/>
+      <c r="C3" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="139"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="138" t="s">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139" t="s">
+      <c r="G3" s="114"/>
+      <c r="H3" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="138" t="s">
+      <c r="I3" s="114"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139" t="s">
+      <c r="L3" s="114"/>
+      <c r="M3" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="140"/>
+      <c r="N3" s="115"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -19672,10 +19672,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="141" t="s">
+      <c r="S3" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="142"/>
+      <c r="T3" s="117"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -19697,10 +19697,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="143" t="s">
+      <c r="R4" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="144"/>
+      <c r="S4" s="119"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -19726,8 +19726,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="146"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="121"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -19750,10 +19750,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="147" t="s">
+      <c r="R6" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="148"/>
+      <c r="S6" s="123"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -19776,10 +19776,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="149" t="s">
+      <c r="R7" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="150"/>
+      <c r="S7" s="125"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -19803,11 +19803,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="151" t="s">
+      <c r="R8" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="152"/>
-      <c r="T8" s="153"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="128"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -19829,10 +19829,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="134" t="s">
+      <c r="R9" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="135"/>
+      <c r="S9" s="110"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -19855,10 +19855,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="130" t="s">
+      <c r="R10" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="131"/>
+      <c r="S10" s="130"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -19879,13 +19879,13 @@
       <c r="M11" s="63"/>
       <c r="N11" s="63"/>
       <c r="O11" s="63"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="132"/>
-      <c r="T11" s="118"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="132"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -19905,234 +19905,287 @@
       <c r="M12" s="61"/>
       <c r="N12" s="61"/>
       <c r="O12" s="61"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="61"/>
       <c r="R12" s="59" t="s">
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="112"/>
+      <c r="T12" s="134"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="120" t="s">
+      <c r="A13" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
-      <c r="P13" s="126"/>
-      <c r="Q13" s="126"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="135"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="128"/>
-      <c r="T13" s="129"/>
+      <c r="S13" s="140"/>
+      <c r="T13" s="141"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="127"/>
-      <c r="Q14" s="127"/>
+      <c r="A14" s="136"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="125"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="125"/>
-      <c r="T15" s="125"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120" t="s">
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="122" t="s">
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="122"/>
-      <c r="Q16" s="122"/>
-      <c r="R16" s="123"/>
-      <c r="S16" s="124" t="s">
+      <c r="P16" s="142"/>
+      <c r="Q16" s="142"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="124"/>
+      <c r="T16" s="144"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="121"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="123" t="s">
+      <c r="A17" s="136"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124" t="s">
+      <c r="P17" s="144"/>
+      <c r="Q17" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="144"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="119"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="148"/>
+      <c r="L18" s="148"/>
+      <c r="M18" s="148"/>
+      <c r="N18" s="148"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="149"/>
+      <c r="Q18" s="149"/>
+      <c r="R18" s="149"/>
+      <c r="S18" s="149"/>
+      <c r="T18" s="149"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="110"/>
+      <c r="A19" s="145"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="110"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110"/>
+      <c r="A20" s="145"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="145"/>
+      <c r="T20" s="145"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
+      <c r="A21" s="151"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="151"/>
+      <c r="I21" s="151"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="151"/>
+      <c r="M21" s="151"/>
+      <c r="N21" s="151"/>
+      <c r="O21" s="153"/>
+      <c r="P21" s="151"/>
+      <c r="Q21" s="151"/>
+      <c r="R21" s="151"/>
+      <c r="S21" s="151"/>
+      <c r="T21" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -20148,62 +20201,9 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="B11:O11">
+  <conditionalFormatting sqref="B11:Q11">
     <cfRule type="cellIs" dxfId="89" priority="3" operator="equal">
       <formula>"연"</formula>
     </cfRule>
@@ -20583,51 +20583,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="136" t="str">
+      <c r="A2" s="111" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="137" t="s">
+      <c r="Q2" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="138" t="s">
+      <c r="A3" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139" t="s">
+      <c r="B3" s="114"/>
+      <c r="C3" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="139"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="138" t="s">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139" t="s">
+      <c r="G3" s="114"/>
+      <c r="H3" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="138" t="s">
+      <c r="I3" s="114"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139" t="s">
+      <c r="L3" s="114"/>
+      <c r="M3" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="140"/>
+      <c r="N3" s="115"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -20639,10 +20639,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="141" t="s">
+      <c r="S3" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="142"/>
+      <c r="T3" s="117"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -20664,10 +20664,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="143" t="s">
+      <c r="R4" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="144"/>
+      <c r="S4" s="119"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -20693,8 +20693,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="146"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="121"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -20717,10 +20717,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="147" t="s">
+      <c r="R6" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="148"/>
+      <c r="S6" s="123"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -20743,10 +20743,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="149" t="s">
+      <c r="R7" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="150"/>
+      <c r="S7" s="125"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -20770,11 +20770,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="151" t="s">
+      <c r="R8" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="152"/>
-      <c r="T8" s="153"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="128"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -20796,10 +20796,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="134" t="s">
+      <c r="R9" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="135"/>
+      <c r="S9" s="110"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -20822,10 +20822,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="130" t="s">
+      <c r="R10" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="131"/>
+      <c r="S10" s="130"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -20846,13 +20846,13 @@
       <c r="M11" s="63"/>
       <c r="N11" s="63"/>
       <c r="O11" s="63"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="132"/>
-      <c r="T11" s="118"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="132"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -20872,234 +20872,287 @@
       <c r="M12" s="61"/>
       <c r="N12" s="61"/>
       <c r="O12" s="61"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="61"/>
       <c r="R12" s="59" t="s">
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="112"/>
+      <c r="T12" s="134"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="120" t="s">
+      <c r="A13" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
-      <c r="P13" s="126"/>
-      <c r="Q13" s="126"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="135"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="128"/>
-      <c r="T13" s="129"/>
+      <c r="S13" s="140"/>
+      <c r="T13" s="141"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="127"/>
-      <c r="Q14" s="127"/>
+      <c r="A14" s="136"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="125"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="125"/>
-      <c r="T15" s="125"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120" t="s">
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="122" t="s">
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="122"/>
-      <c r="Q16" s="122"/>
-      <c r="R16" s="123"/>
-      <c r="S16" s="124" t="s">
+      <c r="P16" s="142"/>
+      <c r="Q16" s="142"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="124"/>
+      <c r="T16" s="144"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="121"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="123" t="s">
+      <c r="A17" s="136"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124" t="s">
+      <c r="P17" s="144"/>
+      <c r="Q17" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="144"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="119"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="148"/>
+      <c r="L18" s="148"/>
+      <c r="M18" s="148"/>
+      <c r="N18" s="148"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="149"/>
+      <c r="Q18" s="149"/>
+      <c r="R18" s="149"/>
+      <c r="S18" s="149"/>
+      <c r="T18" s="149"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="110"/>
+      <c r="A19" s="145"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="110"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110"/>
+      <c r="A20" s="145"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="145"/>
+      <c r="T20" s="145"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
+      <c r="A21" s="151"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="151"/>
+      <c r="I21" s="151"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="151"/>
+      <c r="M21" s="151"/>
+      <c r="N21" s="151"/>
+      <c r="O21" s="153"/>
+      <c r="P21" s="151"/>
+      <c r="Q21" s="151"/>
+      <c r="R21" s="151"/>
+      <c r="S21" s="151"/>
+      <c r="T21" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -21115,62 +21168,9 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="B11:O11">
+  <conditionalFormatting sqref="B11:Q11">
     <cfRule type="cellIs" dxfId="79" priority="3" operator="equal">
       <formula>"연"</formula>
     </cfRule>
@@ -21550,51 +21550,51 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
-      <c r="A2" s="136" t="str">
+      <c r="A2" s="111" t="str">
         <f>"2025년"&amp;[1]default!A1&amp;"월"</f>
         <v>2025년2월</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
       <c r="K2" s="80"/>
       <c r="M2" s="79"/>
       <c r="P2" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="137" t="s">
+      <c r="Q2" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="138" t="s">
+      <c r="A3" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139" t="s">
+      <c r="B3" s="114"/>
+      <c r="C3" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="139"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="138" t="s">
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139" t="s">
+      <c r="G3" s="114"/>
+      <c r="H3" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="138" t="s">
+      <c r="I3" s="114"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139" t="s">
+      <c r="L3" s="114"/>
+      <c r="M3" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="140"/>
+      <c r="N3" s="115"/>
       <c r="O3" s="77" t="s">
         <v>44</v>
       </c>
@@ -21606,10 +21606,10 @@
       <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="141" t="s">
+      <c r="S3" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="142"/>
+      <c r="T3" s="117"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" thickTop="1">
       <c r="A4" s="56" t="s">
@@ -21631,10 +21631,10 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="143" t="s">
+      <c r="R4" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="144"/>
+      <c r="S4" s="119"/>
       <c r="T4" s="73">
         <v>29</v>
       </c>
@@ -21660,8 +21660,8 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="146"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="121"/>
       <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:22" ht="24" customHeight="1">
@@ -21684,10 +21684,10 @@
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
-      <c r="R6" s="147" t="s">
+      <c r="R6" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="148"/>
+      <c r="S6" s="123"/>
       <c r="T6" s="70"/>
     </row>
     <row r="7" spans="1:22" ht="28.5" customHeight="1">
@@ -21710,10 +21710,10 @@
       <c r="O7" s="61"/>
       <c r="P7" s="61"/>
       <c r="Q7" s="60"/>
-      <c r="R7" s="149" t="s">
+      <c r="R7" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="150"/>
+      <c r="S7" s="125"/>
       <c r="T7" s="68"/>
       <c r="V7" s="67"/>
     </row>
@@ -21737,11 +21737,11 @@
       <c r="O8" s="61"/>
       <c r="P8" s="61"/>
       <c r="Q8" s="60"/>
-      <c r="R8" s="151" t="s">
+      <c r="R8" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="S8" s="152"/>
-      <c r="T8" s="153"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="128"/>
     </row>
     <row r="9" spans="1:22" ht="24" customHeight="1">
       <c r="A9" s="55" t="s">
@@ -21763,10 +21763,10 @@
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
       <c r="Q9" s="56"/>
-      <c r="R9" s="134" t="s">
+      <c r="R9" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="135"/>
+      <c r="S9" s="110"/>
       <c r="T9" s="66"/>
     </row>
     <row r="10" spans="1:22" ht="24" customHeight="1">
@@ -21789,10 +21789,10 @@
       <c r="O10" s="55"/>
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
-      <c r="R10" s="130" t="s">
+      <c r="R10" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="131"/>
+      <c r="S10" s="130"/>
       <c r="T10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="24" customHeight="1">
@@ -21813,13 +21813,13 @@
       <c r="M11" s="63"/>
       <c r="N11" s="63"/>
       <c r="O11" s="63"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
       <c r="R11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="S11" s="132"/>
-      <c r="T11" s="118"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="132"/>
     </row>
     <row r="12" spans="1:22" ht="28.5" customHeight="1">
       <c r="A12" s="55" t="s">
@@ -21839,234 +21839,287 @@
       <c r="M12" s="61"/>
       <c r="N12" s="61"/>
       <c r="O12" s="61"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="61"/>
       <c r="R12" s="59" t="s">
         <v>30</v>
       </c>
       <c r="S12" s="133"/>
-      <c r="T12" s="112"/>
+      <c r="T12" s="134"/>
     </row>
     <row r="13" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A13" s="120" t="s">
+      <c r="A13" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
-      <c r="P13" s="126"/>
-      <c r="Q13" s="126"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="135"/>
       <c r="R13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="128"/>
-      <c r="T13" s="129"/>
+      <c r="S13" s="140"/>
+      <c r="T13" s="141"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="127"/>
-      <c r="Q14" s="127"/>
+      <c r="A14" s="136"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
       <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:22" ht="26.25" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="125"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="125"/>
-      <c r="T15" s="125"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120" t="s">
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="122" t="s">
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="122"/>
-      <c r="Q16" s="122"/>
-      <c r="R16" s="123"/>
-      <c r="S16" s="124" t="s">
+      <c r="P16" s="142"/>
+      <c r="Q16" s="142"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="124"/>
+      <c r="T16" s="144"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="121"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="123" t="s">
+      <c r="A17" s="136"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124" t="s">
+      <c r="P17" s="144"/>
+      <c r="Q17" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="144"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="119"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="148"/>
+      <c r="L18" s="148"/>
+      <c r="M18" s="148"/>
+      <c r="N18" s="148"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="149"/>
+      <c r="Q18" s="149"/>
+      <c r="R18" s="149"/>
+      <c r="S18" s="149"/>
+      <c r="T18" s="149"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="110"/>
+      <c r="A19" s="145"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145"/>
     </row>
     <row r="20" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A20" s="110"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110"/>
+      <c r="A20" s="145"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="145"/>
+      <c r="T20" s="145"/>
     </row>
     <row r="21" spans="1:20" ht="29.1" customHeight="1">
-      <c r="A21" s="109"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
+      <c r="A21" s="151"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="151"/>
+      <c r="I21" s="151"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="151"/>
+      <c r="M21" s="151"/>
+      <c r="N21" s="151"/>
+      <c r="O21" s="153"/>
+      <c r="P21" s="151"/>
+      <c r="Q21" s="151"/>
+      <c r="R21" s="151"/>
+      <c r="S21" s="151"/>
+      <c r="T21" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q2:T2"/>
@@ -22082,62 +22135,9 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G17"/>
-    <mergeCell ref="H16:N17"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="B11:O11">
+  <conditionalFormatting sqref="B11:Q11">
     <cfRule type="cellIs" dxfId="69" priority="3" operator="equal">
       <formula>"연"</formula>
     </cfRule>
